--- a/BWI/bestwine_output/bestwine_Finland.xlsx
+++ b/BWI/bestwine_output/bestwine_Finland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA203"/>
+  <dimension ref="A1:AA209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -23824,6 +23824,724 @@
         </is>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Winestate Oy</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>Winestate Oy</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>4072</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>22 Porkkalankatu</t>
+        </is>
+      </c>
+      <c r="H204" s="2" t="inlineStr">
+        <is>
+          <t>00180</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winestate.fi</t>
+        </is>
+      </c>
+      <c r="J204" s="2" t="inlineStr"/>
+      <c r="K204" s="2" t="inlineStr"/>
+      <c r="L204" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M204" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N204" s="2" t="inlineStr">
+        <is>
+          <t>products@winestate.fi</t>
+        </is>
+      </c>
+      <c r="O204" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 5658900</t>
+        </is>
+      </c>
+      <c r="P204" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q204" s="2" t="inlineStr">
+        <is>
+          <t>19544710</t>
+        </is>
+      </c>
+      <c r="R204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winestate-oy</t>
+        </is>
+      </c>
+      <c r="S204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winestatepro/</t>
+        </is>
+      </c>
+      <c r="T204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winestate.fi/</t>
+        </is>
+      </c>
+      <c r="U204" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/winestate</t>
+        </is>
+      </c>
+      <c r="V204" s="2" t="inlineStr"/>
+      <c r="W204" s="2" t="inlineStr">
+        <is>
+          <t>Mikko Hintikka</t>
+        </is>
+      </c>
+      <c r="X204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Sales Director</t>
+        </is>
+      </c>
+      <c r="Y204" s="2" t="inlineStr"/>
+      <c r="Z204" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA204" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mikko-hintikka-420409a7/</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Winestate Oy</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>Winestate Oy</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>4072</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>22 Porkkalankatu</t>
+        </is>
+      </c>
+      <c r="H205" s="2" t="inlineStr">
+        <is>
+          <t>00180</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winestate.fi</t>
+        </is>
+      </c>
+      <c r="J205" s="2" t="inlineStr"/>
+      <c r="K205" s="2" t="inlineStr"/>
+      <c r="L205" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M205" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N205" s="2" t="inlineStr">
+        <is>
+          <t>products@winestate.fi</t>
+        </is>
+      </c>
+      <c r="O205" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 5658900</t>
+        </is>
+      </c>
+      <c r="P205" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q205" s="2" t="inlineStr">
+        <is>
+          <t>19544710</t>
+        </is>
+      </c>
+      <c r="R205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winestate-oy</t>
+        </is>
+      </c>
+      <c r="S205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winestatepro/</t>
+        </is>
+      </c>
+      <c r="T205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winestate.fi/</t>
+        </is>
+      </c>
+      <c r="U205" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/winestate</t>
+        </is>
+      </c>
+      <c r="V205" s="2" t="inlineStr"/>
+      <c r="W205" s="2" t="inlineStr">
+        <is>
+          <t>Salla Salminen</t>
+        </is>
+      </c>
+      <c r="X205" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y205" s="2" t="inlineStr"/>
+      <c r="Z205" s="2" t="inlineStr"/>
+      <c r="AA205" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/salla-salminen-3a245582/</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Winestate Oy</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>Winestate Oy</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>4072</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>22 Porkkalankatu</t>
+        </is>
+      </c>
+      <c r="H206" s="2" t="inlineStr">
+        <is>
+          <t>00180</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winestate.fi</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr"/>
+      <c r="K206" s="2" t="inlineStr"/>
+      <c r="L206" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M206" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N206" s="2" t="inlineStr">
+        <is>
+          <t>products@winestate.fi</t>
+        </is>
+      </c>
+      <c r="O206" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 5658900</t>
+        </is>
+      </c>
+      <c r="P206" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q206" s="2" t="inlineStr">
+        <is>
+          <t>19544710</t>
+        </is>
+      </c>
+      <c r="R206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winestate-oy</t>
+        </is>
+      </c>
+      <c r="S206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winestatepro/</t>
+        </is>
+      </c>
+      <c r="T206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winestate.fi/</t>
+        </is>
+      </c>
+      <c r="U206" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/winestate</t>
+        </is>
+      </c>
+      <c r="V206" s="2" t="inlineStr"/>
+      <c r="W206" s="2" t="inlineStr">
+        <is>
+          <t>Annastiina Jäppinen</t>
+        </is>
+      </c>
+      <c r="X206" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager &amp; Partner</t>
+        </is>
+      </c>
+      <c r="Y206" s="2" t="inlineStr"/>
+      <c r="Z206" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA206" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/annastiina-j%C3%A4ppinen-8aa9b847/</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Winestate Oy</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>Winestate Oy</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>4072</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>22 Porkkalankatu</t>
+        </is>
+      </c>
+      <c r="H207" s="2" t="inlineStr">
+        <is>
+          <t>00180</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winestate.fi</t>
+        </is>
+      </c>
+      <c r="J207" s="2" t="inlineStr"/>
+      <c r="K207" s="2" t="inlineStr"/>
+      <c r="L207" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M207" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N207" s="2" t="inlineStr">
+        <is>
+          <t>products@winestate.fi</t>
+        </is>
+      </c>
+      <c r="O207" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 5658900</t>
+        </is>
+      </c>
+      <c r="P207" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q207" s="2" t="inlineStr">
+        <is>
+          <t>19544710</t>
+        </is>
+      </c>
+      <c r="R207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winestate-oy</t>
+        </is>
+      </c>
+      <c r="S207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winestatepro/</t>
+        </is>
+      </c>
+      <c r="T207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winestate.fi/</t>
+        </is>
+      </c>
+      <c r="U207" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/winestate</t>
+        </is>
+      </c>
+      <c r="V207" s="2" t="inlineStr"/>
+      <c r="W207" s="2" t="inlineStr">
+        <is>
+          <t>Anssi Lehtinen</t>
+        </is>
+      </c>
+      <c r="X207" s="2" t="inlineStr">
+        <is>
+          <t>Key Account Manager</t>
+        </is>
+      </c>
+      <c r="Y207" s="2" t="inlineStr"/>
+      <c r="Z207" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA207" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anssi-lehtinen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Winestate Oy</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>Winestate Oy</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>4072</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G208" s="2" t="inlineStr">
+        <is>
+          <t>22 Porkkalankatu</t>
+        </is>
+      </c>
+      <c r="H208" s="2" t="inlineStr">
+        <is>
+          <t>00180</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winestate.fi</t>
+        </is>
+      </c>
+      <c r="J208" s="2" t="inlineStr"/>
+      <c r="K208" s="2" t="inlineStr"/>
+      <c r="L208" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M208" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N208" s="2" t="inlineStr">
+        <is>
+          <t>products@winestate.fi</t>
+        </is>
+      </c>
+      <c r="O208" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 5658900</t>
+        </is>
+      </c>
+      <c r="P208" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q208" s="2" t="inlineStr">
+        <is>
+          <t>19544710</t>
+        </is>
+      </c>
+      <c r="R208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winestate-oy</t>
+        </is>
+      </c>
+      <c r="S208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winestatepro/</t>
+        </is>
+      </c>
+      <c r="T208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winestate.fi/</t>
+        </is>
+      </c>
+      <c r="U208" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/winestate</t>
+        </is>
+      </c>
+      <c r="V208" s="2" t="inlineStr"/>
+      <c r="W208" s="2" t="inlineStr">
+        <is>
+          <t>Katariina Immonen</t>
+        </is>
+      </c>
+      <c r="X208" s="2" t="inlineStr">
+        <is>
+          <t>Key Account Manager</t>
+        </is>
+      </c>
+      <c r="Y208" s="2" t="inlineStr"/>
+      <c r="Z208" s="2" t="inlineStr"/>
+      <c r="AA208" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/katariina-immonen-132a7997/</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Winestate Oy</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>Winestate Oy</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>4072</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G209" s="2" t="inlineStr">
+        <is>
+          <t>22 Porkkalankatu</t>
+        </is>
+      </c>
+      <c r="H209" s="2" t="inlineStr">
+        <is>
+          <t>00180</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winestate.fi</t>
+        </is>
+      </c>
+      <c r="J209" s="2" t="inlineStr"/>
+      <c r="K209" s="2" t="inlineStr"/>
+      <c r="L209" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M209" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N209" s="2" t="inlineStr">
+        <is>
+          <t>products@winestate.fi</t>
+        </is>
+      </c>
+      <c r="O209" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 5658900</t>
+        </is>
+      </c>
+      <c r="P209" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q209" s="2" t="inlineStr">
+        <is>
+          <t>19544710</t>
+        </is>
+      </c>
+      <c r="R209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winestate-oy</t>
+        </is>
+      </c>
+      <c r="S209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winestatepro/</t>
+        </is>
+      </c>
+      <c r="T209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winestate.fi/</t>
+        </is>
+      </c>
+      <c r="U209" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/winestate</t>
+        </is>
+      </c>
+      <c r="V209" s="2" t="inlineStr"/>
+      <c r="W209" s="2" t="inlineStr">
+        <is>
+          <t>Frank Forssell</t>
+        </is>
+      </c>
+      <c r="X209" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y209" s="2" t="inlineStr"/>
+      <c r="Z209" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA209" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/frank-forssell-a7b4a14/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Finland.xlsx
+++ b/BWI/bestwine_output/bestwine_Finland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA209"/>
+  <dimension ref="A1:AA215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -24542,6 +24542,724 @@
         </is>
       </c>
     </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Winestate Oy</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>Winestate Oy</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>4072</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G210" s="2" t="inlineStr">
+        <is>
+          <t>22 Porkkalankatu</t>
+        </is>
+      </c>
+      <c r="H210" s="2" t="inlineStr">
+        <is>
+          <t>00180</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winestate.fi</t>
+        </is>
+      </c>
+      <c r="J210" s="2" t="inlineStr"/>
+      <c r="K210" s="2" t="inlineStr"/>
+      <c r="L210" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M210" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N210" s="2" t="inlineStr">
+        <is>
+          <t>products@winestate.fi</t>
+        </is>
+      </c>
+      <c r="O210" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 5658900</t>
+        </is>
+      </c>
+      <c r="P210" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q210" s="2" t="inlineStr">
+        <is>
+          <t>19544710</t>
+        </is>
+      </c>
+      <c r="R210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winestate-oy</t>
+        </is>
+      </c>
+      <c r="S210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winestatepro/</t>
+        </is>
+      </c>
+      <c r="T210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winestate.fi/</t>
+        </is>
+      </c>
+      <c r="U210" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/winestate</t>
+        </is>
+      </c>
+      <c r="V210" s="2" t="inlineStr"/>
+      <c r="W210" s="2" t="inlineStr">
+        <is>
+          <t>Mikko Hintikka</t>
+        </is>
+      </c>
+      <c r="X210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Sales Director</t>
+        </is>
+      </c>
+      <c r="Y210" s="2" t="inlineStr"/>
+      <c r="Z210" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA210" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mikko-hintikka-420409a7/</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Winestate Oy</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>Winestate Oy</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>4072</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>22 Porkkalankatu</t>
+        </is>
+      </c>
+      <c r="H211" s="2" t="inlineStr">
+        <is>
+          <t>00180</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winestate.fi</t>
+        </is>
+      </c>
+      <c r="J211" s="2" t="inlineStr"/>
+      <c r="K211" s="2" t="inlineStr"/>
+      <c r="L211" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M211" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N211" s="2" t="inlineStr">
+        <is>
+          <t>products@winestate.fi</t>
+        </is>
+      </c>
+      <c r="O211" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 5658900</t>
+        </is>
+      </c>
+      <c r="P211" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q211" s="2" t="inlineStr">
+        <is>
+          <t>19544710</t>
+        </is>
+      </c>
+      <c r="R211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winestate-oy</t>
+        </is>
+      </c>
+      <c r="S211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winestatepro/</t>
+        </is>
+      </c>
+      <c r="T211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winestate.fi/</t>
+        </is>
+      </c>
+      <c r="U211" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/winestate</t>
+        </is>
+      </c>
+      <c r="V211" s="2" t="inlineStr"/>
+      <c r="W211" s="2" t="inlineStr">
+        <is>
+          <t>Salla Salminen</t>
+        </is>
+      </c>
+      <c r="X211" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y211" s="2" t="inlineStr"/>
+      <c r="Z211" s="2" t="inlineStr"/>
+      <c r="AA211" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/salla-salminen-3a245582/</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Winestate Oy</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>Winestate Oy</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>4072</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>22 Porkkalankatu</t>
+        </is>
+      </c>
+      <c r="H212" s="2" t="inlineStr">
+        <is>
+          <t>00180</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winestate.fi</t>
+        </is>
+      </c>
+      <c r="J212" s="2" t="inlineStr"/>
+      <c r="K212" s="2" t="inlineStr"/>
+      <c r="L212" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M212" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N212" s="2" t="inlineStr">
+        <is>
+          <t>products@winestate.fi</t>
+        </is>
+      </c>
+      <c r="O212" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 5658900</t>
+        </is>
+      </c>
+      <c r="P212" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q212" s="2" t="inlineStr">
+        <is>
+          <t>19544710</t>
+        </is>
+      </c>
+      <c r="R212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winestate-oy</t>
+        </is>
+      </c>
+      <c r="S212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winestatepro/</t>
+        </is>
+      </c>
+      <c r="T212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winestate.fi/</t>
+        </is>
+      </c>
+      <c r="U212" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/winestate</t>
+        </is>
+      </c>
+      <c r="V212" s="2" t="inlineStr"/>
+      <c r="W212" s="2" t="inlineStr">
+        <is>
+          <t>Annastiina Jäppinen</t>
+        </is>
+      </c>
+      <c r="X212" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager &amp; Partner</t>
+        </is>
+      </c>
+      <c r="Y212" s="2" t="inlineStr"/>
+      <c r="Z212" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA212" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/annastiina-j%C3%A4ppinen-8aa9b847/</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>Winestate Oy</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>Winestate Oy</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>4072</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>22 Porkkalankatu</t>
+        </is>
+      </c>
+      <c r="H213" s="2" t="inlineStr">
+        <is>
+          <t>00180</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winestate.fi</t>
+        </is>
+      </c>
+      <c r="J213" s="2" t="inlineStr"/>
+      <c r="K213" s="2" t="inlineStr"/>
+      <c r="L213" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M213" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N213" s="2" t="inlineStr">
+        <is>
+          <t>products@winestate.fi</t>
+        </is>
+      </c>
+      <c r="O213" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 5658900</t>
+        </is>
+      </c>
+      <c r="P213" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q213" s="2" t="inlineStr">
+        <is>
+          <t>19544710</t>
+        </is>
+      </c>
+      <c r="R213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winestate-oy</t>
+        </is>
+      </c>
+      <c r="S213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winestatepro/</t>
+        </is>
+      </c>
+      <c r="T213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winestate.fi/</t>
+        </is>
+      </c>
+      <c r="U213" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/winestate</t>
+        </is>
+      </c>
+      <c r="V213" s="2" t="inlineStr"/>
+      <c r="W213" s="2" t="inlineStr">
+        <is>
+          <t>Anssi Lehtinen</t>
+        </is>
+      </c>
+      <c r="X213" s="2" t="inlineStr">
+        <is>
+          <t>Key Account Manager</t>
+        </is>
+      </c>
+      <c r="Y213" s="2" t="inlineStr"/>
+      <c r="Z213" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA213" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anssi-lehtinen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Winestate Oy</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>Winestate Oy</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>4072</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>22 Porkkalankatu</t>
+        </is>
+      </c>
+      <c r="H214" s="2" t="inlineStr">
+        <is>
+          <t>00180</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winestate.fi</t>
+        </is>
+      </c>
+      <c r="J214" s="2" t="inlineStr"/>
+      <c r="K214" s="2" t="inlineStr"/>
+      <c r="L214" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M214" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N214" s="2" t="inlineStr">
+        <is>
+          <t>products@winestate.fi</t>
+        </is>
+      </c>
+      <c r="O214" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 5658900</t>
+        </is>
+      </c>
+      <c r="P214" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q214" s="2" t="inlineStr">
+        <is>
+          <t>19544710</t>
+        </is>
+      </c>
+      <c r="R214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winestate-oy</t>
+        </is>
+      </c>
+      <c r="S214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winestatepro/</t>
+        </is>
+      </c>
+      <c r="T214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winestate.fi/</t>
+        </is>
+      </c>
+      <c r="U214" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/winestate</t>
+        </is>
+      </c>
+      <c r="V214" s="2" t="inlineStr"/>
+      <c r="W214" s="2" t="inlineStr">
+        <is>
+          <t>Katariina Immonen</t>
+        </is>
+      </c>
+      <c r="X214" s="2" t="inlineStr">
+        <is>
+          <t>Key Account Manager</t>
+        </is>
+      </c>
+      <c r="Y214" s="2" t="inlineStr"/>
+      <c r="Z214" s="2" t="inlineStr"/>
+      <c r="AA214" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/katariina-immonen-132a7997/</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>Winestate Oy</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>Winestate Oy</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>4072</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>22 Porkkalankatu</t>
+        </is>
+      </c>
+      <c r="H215" s="2" t="inlineStr">
+        <is>
+          <t>00180</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winestate.fi</t>
+        </is>
+      </c>
+      <c r="J215" s="2" t="inlineStr"/>
+      <c r="K215" s="2" t="inlineStr"/>
+      <c r="L215" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M215" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N215" s="2" t="inlineStr">
+        <is>
+          <t>products@winestate.fi</t>
+        </is>
+      </c>
+      <c r="O215" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 5658900</t>
+        </is>
+      </c>
+      <c r="P215" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q215" s="2" t="inlineStr">
+        <is>
+          <t>19544710</t>
+        </is>
+      </c>
+      <c r="R215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/winestate-oy</t>
+        </is>
+      </c>
+      <c r="S215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winestatepro/</t>
+        </is>
+      </c>
+      <c r="T215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winestate.fi/</t>
+        </is>
+      </c>
+      <c r="U215" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/winestate</t>
+        </is>
+      </c>
+      <c r="V215" s="2" t="inlineStr"/>
+      <c r="W215" s="2" t="inlineStr">
+        <is>
+          <t>Frank Forssell</t>
+        </is>
+      </c>
+      <c r="X215" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y215" s="2" t="inlineStr"/>
+      <c r="Z215" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA215" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/frank-forssell-a7b4a14/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Finland.xlsx
+++ b/BWI/bestwine_output/bestwine_Finland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA215"/>
+  <dimension ref="A1:AA225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -25260,6 +25260,1052 @@
         </is>
       </c>
     </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Let Me Wine Oy</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>Let Me Wine Oy</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>40821</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>10 Vironkatu</t>
+        </is>
+      </c>
+      <c r="H216" s="2" t="inlineStr">
+        <is>
+          <t>00170</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.letme.fi</t>
+        </is>
+      </c>
+      <c r="J216" s="2" t="inlineStr"/>
+      <c r="K216" s="2" t="inlineStr"/>
+      <c r="L216" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="inlineStr"/>
+      <c r="N216" s="2" t="inlineStr">
+        <is>
+          <t>toni@letme.fi</t>
+        </is>
+      </c>
+      <c r="O216" s="2" t="inlineStr"/>
+      <c r="P216" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q216" s="2" t="inlineStr">
+        <is>
+          <t>28373351</t>
+        </is>
+      </c>
+      <c r="R216" s="2" t="inlineStr"/>
+      <c r="S216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/letmewinehelsinki</t>
+        </is>
+      </c>
+      <c r="T216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/letme.fi/</t>
+        </is>
+      </c>
+      <c r="U216" s="2" t="inlineStr"/>
+      <c r="V216" s="2" t="inlineStr"/>
+      <c r="W216" s="2" t="inlineStr">
+        <is>
+          <t>Toni Feri</t>
+        </is>
+      </c>
+      <c r="X216" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="Y216" s="2" t="inlineStr"/>
+      <c r="Z216" s="2" t="inlineStr"/>
+      <c r="AA216" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/toni-feri-3548171b4/?originalSubdomain=fi</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Thirsty Bear Oy</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>Thirsty Bear Oy</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>35662</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>7 Lönnrotinkatu</t>
+        </is>
+      </c>
+      <c r="H217" s="2" t="inlineStr">
+        <is>
+          <t>00120</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thirstybear.fi</t>
+        </is>
+      </c>
+      <c r="J217" s="2" t="inlineStr"/>
+      <c r="K217" s="2" t="inlineStr"/>
+      <c r="L217" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M217" s="2" t="inlineStr"/>
+      <c r="N217" s="2" t="inlineStr">
+        <is>
+          <t>info@thirstybear.fi</t>
+        </is>
+      </c>
+      <c r="O217" s="2" t="inlineStr"/>
+      <c r="P217" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q217" s="2" t="inlineStr">
+        <is>
+          <t>32653196</t>
+        </is>
+      </c>
+      <c r="R217" s="2" t="inlineStr"/>
+      <c r="S217" s="2" t="inlineStr"/>
+      <c r="T217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thirstybearwines/</t>
+        </is>
+      </c>
+      <c r="U217" s="2" t="inlineStr"/>
+      <c r="V217" s="2" t="inlineStr"/>
+      <c r="W217" s="2" t="inlineStr">
+        <is>
+          <t>Tom Murray</t>
+        </is>
+      </c>
+      <c r="X217" s="2" t="inlineStr">
+        <is>
+          <t>Owner and Founder</t>
+        </is>
+      </c>
+      <c r="Y217" s="2" t="inlineStr"/>
+      <c r="Z217" s="2" t="inlineStr"/>
+      <c r="AA217" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tommurraywillis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Mercantem Oy</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>Mercantem Oy</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>23325</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>Kirkkonummi</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>5 Luostarinportti</t>
+        </is>
+      </c>
+      <c r="H218" s="2" t="inlineStr">
+        <is>
+          <t>02400</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>https://lasso.fi</t>
+        </is>
+      </c>
+      <c r="J218" s="2" t="inlineStr"/>
+      <c r="K218" s="2" t="inlineStr"/>
+      <c r="L218" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M218" s="2" t="inlineStr"/>
+      <c r="N218" s="2" t="inlineStr">
+        <is>
+          <t>info@lasso.fi</t>
+        </is>
+      </c>
+      <c r="O218" s="2" t="inlineStr">
+        <is>
+          <t>+358 10 4006482</t>
+        </is>
+      </c>
+      <c r="P218" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q218" s="2" t="inlineStr">
+        <is>
+          <t>19067942</t>
+        </is>
+      </c>
+      <c r="R218" s="2" t="inlineStr"/>
+      <c r="S218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lassodrinks.fi/</t>
+        </is>
+      </c>
+      <c r="T218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lasso_drinks</t>
+        </is>
+      </c>
+      <c r="U218" s="2" t="inlineStr"/>
+      <c r="V218" s="2" t="inlineStr"/>
+      <c r="W218" s="2" t="inlineStr">
+        <is>
+          <t>Kimmo Koivikko</t>
+        </is>
+      </c>
+      <c r="X218" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; Ceo</t>
+        </is>
+      </c>
+      <c r="Y218" s="2" t="inlineStr"/>
+      <c r="Z218" s="2" t="inlineStr"/>
+      <c r="AA218" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kimmo-koivikko-51b3b51/</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>Muru Wines Oy</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>Muru Wines Oy</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>41391</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa</t>
+        </is>
+      </c>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>Pulttitie 4</t>
+        </is>
+      </c>
+      <c r="H219" s="2" t="inlineStr">
+        <is>
+          <t>00880</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>https://muruwines.fi</t>
+        </is>
+      </c>
+      <c r="J219" s="2" t="inlineStr"/>
+      <c r="K219" s="2" t="inlineStr"/>
+      <c r="L219" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M219" s="2" t="inlineStr"/>
+      <c r="N219" s="2" t="inlineStr">
+        <is>
+          <t>tilaukset@muruwines.fi</t>
+        </is>
+      </c>
+      <c r="O219" s="2" t="inlineStr"/>
+      <c r="P219" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q219" s="2" t="inlineStr">
+        <is>
+          <t>29433328</t>
+        </is>
+      </c>
+      <c r="R219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/muru-wines-oy/</t>
+        </is>
+      </c>
+      <c r="S219" s="2" t="inlineStr"/>
+      <c r="T219" s="2" t="inlineStr"/>
+      <c r="U219" s="2" t="inlineStr"/>
+      <c r="V219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UC5_6lAG5z45e9FRi8ewWZMw</t>
+        </is>
+      </c>
+      <c r="W219" s="2" t="inlineStr">
+        <is>
+          <t>Mikko Haakana</t>
+        </is>
+      </c>
+      <c r="X219" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner</t>
+        </is>
+      </c>
+      <c r="Y219" s="2" t="inlineStr"/>
+      <c r="Z219" s="2" t="inlineStr"/>
+      <c r="AA219" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mikko-haakana-8b68a913a</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J220" s="2" t="inlineStr"/>
+      <c r="K220" s="2" t="inlineStr"/>
+      <c r="L220" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M220" s="2" t="inlineStr"/>
+      <c r="N220" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O220" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P220" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q220" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T220" s="2" t="inlineStr"/>
+      <c r="U220" s="2" t="inlineStr"/>
+      <c r="V220" s="2" t="inlineStr"/>
+      <c r="W220" s="2" t="inlineStr">
+        <is>
+          <t>Timo Laurila</t>
+        </is>
+      </c>
+      <c r="X220" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Director</t>
+        </is>
+      </c>
+      <c r="Y220" s="2" t="inlineStr"/>
+      <c r="Z220" s="2" t="inlineStr"/>
+      <c r="AA220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/timo-laurila-947078a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J221" s="2" t="inlineStr"/>
+      <c r="K221" s="2" t="inlineStr"/>
+      <c r="L221" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M221" s="2" t="inlineStr"/>
+      <c r="N221" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O221" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P221" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q221" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T221" s="2" t="inlineStr"/>
+      <c r="U221" s="2" t="inlineStr"/>
+      <c r="V221" s="2" t="inlineStr"/>
+      <c r="W221" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Jones</t>
+        </is>
+      </c>
+      <c r="X221" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y221" s="2" t="inlineStr"/>
+      <c r="Z221" s="2" t="inlineStr"/>
+      <c r="AA221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patrick-jones-162a875/</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J222" s="2" t="inlineStr"/>
+      <c r="K222" s="2" t="inlineStr"/>
+      <c r="L222" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M222" s="2" t="inlineStr"/>
+      <c r="N222" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O222" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P222" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q222" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T222" s="2" t="inlineStr"/>
+      <c r="U222" s="2" t="inlineStr"/>
+      <c r="V222" s="2" t="inlineStr"/>
+      <c r="W222" s="2" t="inlineStr">
+        <is>
+          <t>Timo Vainonen</t>
+        </is>
+      </c>
+      <c r="X222" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y222" s="2" t="inlineStr"/>
+      <c r="Z222" s="2" t="inlineStr"/>
+      <c r="AA222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/timo-vainonen-348b0521/</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Oy Vindirekt Finland Ab</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>Oy Vindirekt Finland Ab</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>20481</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>22E Sörnäisten rantatie</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>00540</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vindirekt.fi</t>
+        </is>
+      </c>
+      <c r="J223" s="2" t="inlineStr"/>
+      <c r="K223" s="2" t="inlineStr"/>
+      <c r="L223" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M223" s="2" t="inlineStr"/>
+      <c r="N223" s="2" t="inlineStr">
+        <is>
+          <t>vindirekt@vindirekt.fi</t>
+        </is>
+      </c>
+      <c r="O223" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 7745930</t>
+        </is>
+      </c>
+      <c r="P223" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q223" s="2" t="inlineStr">
+        <is>
+          <t>14926170</t>
+        </is>
+      </c>
+      <c r="R223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vindirekt/</t>
+        </is>
+      </c>
+      <c r="S223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vindirekt-111148538919790/</t>
+        </is>
+      </c>
+      <c r="T223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vindirektfinland</t>
+        </is>
+      </c>
+      <c r="U223" s="2" t="inlineStr"/>
+      <c r="V223" s="2" t="inlineStr"/>
+      <c r="W223" s="2" t="inlineStr">
+        <is>
+          <t>Oskari Kaikkonen</t>
+        </is>
+      </c>
+      <c r="X223" s="2" t="inlineStr">
+        <is>
+          <t>Portfolio Manager</t>
+        </is>
+      </c>
+      <c r="Y223" s="2" t="inlineStr"/>
+      <c r="Z223" s="2" t="inlineStr"/>
+      <c r="AA223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/oskari-kaikkonen-59791280/</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Oy Vindirekt Finland Ab</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>Oy Vindirekt Finland Ab</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>20481</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>22E Sörnäisten rantatie</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>00540</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vindirekt.fi</t>
+        </is>
+      </c>
+      <c r="J224" s="2" t="inlineStr"/>
+      <c r="K224" s="2" t="inlineStr"/>
+      <c r="L224" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M224" s="2" t="inlineStr"/>
+      <c r="N224" s="2" t="inlineStr">
+        <is>
+          <t>vindirekt@vindirekt.fi</t>
+        </is>
+      </c>
+      <c r="O224" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 7745930</t>
+        </is>
+      </c>
+      <c r="P224" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q224" s="2" t="inlineStr">
+        <is>
+          <t>14926170</t>
+        </is>
+      </c>
+      <c r="R224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vindirekt/</t>
+        </is>
+      </c>
+      <c r="S224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vindirekt-111148538919790/</t>
+        </is>
+      </c>
+      <c r="T224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vindirektfinland</t>
+        </is>
+      </c>
+      <c r="U224" s="2" t="inlineStr"/>
+      <c r="V224" s="2" t="inlineStr"/>
+      <c r="W224" s="2" t="inlineStr">
+        <is>
+          <t>Ville Tuomola</t>
+        </is>
+      </c>
+      <c r="X224" s="2" t="inlineStr">
+        <is>
+          <t>Senior Sales Professional</t>
+        </is>
+      </c>
+      <c r="Y224" s="2" t="inlineStr"/>
+      <c r="Z224" s="2" t="inlineStr"/>
+      <c r="AA224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ville-tuomola-5a8b5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>Oy Vindirekt Finland Ab</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>Oy Vindirekt Finland Ab</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>20481</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>22E Sörnäisten rantatie</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>00540</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.vindirekt.fi</t>
+        </is>
+      </c>
+      <c r="J225" s="2" t="inlineStr"/>
+      <c r="K225" s="2" t="inlineStr"/>
+      <c r="L225" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M225" s="2" t="inlineStr"/>
+      <c r="N225" s="2" t="inlineStr">
+        <is>
+          <t>vindirekt@vindirekt.fi</t>
+        </is>
+      </c>
+      <c r="O225" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 7745930</t>
+        </is>
+      </c>
+      <c r="P225" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q225" s="2" t="inlineStr">
+        <is>
+          <t>14926170</t>
+        </is>
+      </c>
+      <c r="R225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vindirekt/</t>
+        </is>
+      </c>
+      <c r="S225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vindirekt-111148538919790/</t>
+        </is>
+      </c>
+      <c r="T225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vindirektfinland</t>
+        </is>
+      </c>
+      <c r="U225" s="2" t="inlineStr"/>
+      <c r="V225" s="2" t="inlineStr"/>
+      <c r="W225" s="2" t="inlineStr">
+        <is>
+          <t>Aleksi Lahdenoja</t>
+        </is>
+      </c>
+      <c r="X225" s="2" t="inlineStr">
+        <is>
+          <t>Sales Professional</t>
+        </is>
+      </c>
+      <c r="Y225" s="2" t="inlineStr"/>
+      <c r="Z225" s="2" t="inlineStr"/>
+      <c r="AA225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aleksi-lahdenoja-70859651/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Finland.xlsx
+++ b/BWI/bestwine_output/bestwine_Finland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA225"/>
+  <dimension ref="A1:AA230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -26306,6 +26306,499 @@
         </is>
       </c>
     </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Cisa Drinks Oy</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>Cisa Drinks Oy</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>4020</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>Espoo</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>15 Kavallinmäki</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>02710</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cisa.fi</t>
+        </is>
+      </c>
+      <c r="J226" s="2" t="inlineStr"/>
+      <c r="K226" s="2" t="inlineStr"/>
+      <c r="L226" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M226" s="2" t="inlineStr"/>
+      <c r="N226" s="2" t="inlineStr">
+        <is>
+          <t>info@cisa.fi</t>
+        </is>
+      </c>
+      <c r="O226" s="2" t="inlineStr"/>
+      <c r="P226" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q226" s="2" t="inlineStr">
+        <is>
+          <t>18254850</t>
+        </is>
+      </c>
+      <c r="R226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cisa-drinks-oy/</t>
+        </is>
+      </c>
+      <c r="S226" s="2" t="inlineStr"/>
+      <c r="T226" s="2" t="inlineStr"/>
+      <c r="U226" s="2" t="inlineStr"/>
+      <c r="V226" s="2" t="inlineStr"/>
+      <c r="W226" s="2" t="inlineStr">
+        <is>
+          <t>Risto Suomio</t>
+        </is>
+      </c>
+      <c r="X226" s="2" t="inlineStr">
+        <is>
+          <t>Partner, Purchasing</t>
+        </is>
+      </c>
+      <c r="Y226" s="2" t="inlineStr"/>
+      <c r="Z226" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/risto-suomio-2366702/</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Cisa Drinks Oy</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>Cisa Drinks Oy</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>4020</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>Espoo</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>15 Kavallinmäki</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>02710</t>
+        </is>
+      </c>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cisa.fi</t>
+        </is>
+      </c>
+      <c r="J227" s="2" t="inlineStr"/>
+      <c r="K227" s="2" t="inlineStr"/>
+      <c r="L227" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M227" s="2" t="inlineStr"/>
+      <c r="N227" s="2" t="inlineStr">
+        <is>
+          <t>info@cisa.fi</t>
+        </is>
+      </c>
+      <c r="O227" s="2" t="inlineStr"/>
+      <c r="P227" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q227" s="2" t="inlineStr">
+        <is>
+          <t>18254850</t>
+        </is>
+      </c>
+      <c r="R227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cisa-drinks-oy/</t>
+        </is>
+      </c>
+      <c r="S227" s="2" t="inlineStr"/>
+      <c r="T227" s="2" t="inlineStr"/>
+      <c r="U227" s="2" t="inlineStr"/>
+      <c r="V227" s="2" t="inlineStr"/>
+      <c r="W227" s="2" t="inlineStr">
+        <is>
+          <t>Toni Vaskivuo</t>
+        </is>
+      </c>
+      <c r="X227" s="2" t="inlineStr">
+        <is>
+          <t>Logistics Controller, Buyer</t>
+        </is>
+      </c>
+      <c r="Y227" s="2" t="inlineStr"/>
+      <c r="Z227" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/toni-vaskivuo-604727a4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Wineworld Finland Oy</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>Wineworld Finland Oy</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>35602</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>1 Kaapeliaukio</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>00180</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>https://wineworld.fi</t>
+        </is>
+      </c>
+      <c r="J228" s="2" t="inlineStr"/>
+      <c r="K228" s="2" t="inlineStr"/>
+      <c r="L228" s="2" t="inlineStr"/>
+      <c r="M228" s="2" t="inlineStr"/>
+      <c r="N228" s="2" t="inlineStr">
+        <is>
+          <t>info@wineworld.fi</t>
+        </is>
+      </c>
+      <c r="O228" s="2" t="inlineStr"/>
+      <c r="P228" s="2" t="inlineStr"/>
+      <c r="Q228" s="2" t="inlineStr"/>
+      <c r="R228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wineworld-finland/</t>
+        </is>
+      </c>
+      <c r="S228" s="2" t="inlineStr"/>
+      <c r="T228" s="2" t="inlineStr"/>
+      <c r="U228" s="2" t="inlineStr"/>
+      <c r="V228" s="2" t="inlineStr"/>
+      <c r="W228" s="2" t="inlineStr"/>
+      <c r="X228" s="2" t="inlineStr"/>
+      <c r="Y228" s="2" t="inlineStr"/>
+      <c r="Z228" s="2" t="inlineStr"/>
+      <c r="AA228" s="2" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Diamond Beverages Oy</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>Diamond Beverages Oy</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>23099</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>Vantaa</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>8a Äyritie</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>01510</t>
+        </is>
+      </c>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>https://diamondbeverages.fi</t>
+        </is>
+      </c>
+      <c r="J229" s="2" t="inlineStr"/>
+      <c r="K229" s="2" t="inlineStr"/>
+      <c r="L229" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M229" s="2" t="inlineStr"/>
+      <c r="N229" s="2" t="inlineStr">
+        <is>
+          <t>diamondbeer@diamondbeverages.fi</t>
+        </is>
+      </c>
+      <c r="O229" s="2" t="inlineStr">
+        <is>
+          <t>+358 10 2310801</t>
+        </is>
+      </c>
+      <c r="P229" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q229" s="2" t="inlineStr">
+        <is>
+          <t>14546792</t>
+        </is>
+      </c>
+      <c r="R229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/diamond-beverages-oy</t>
+        </is>
+      </c>
+      <c r="S229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DiamondBeverages/</t>
+        </is>
+      </c>
+      <c r="T229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/diamondbeverages</t>
+        </is>
+      </c>
+      <c r="U229" s="2" t="inlineStr"/>
+      <c r="V229" s="2" t="inlineStr"/>
+      <c r="W229" s="2" t="inlineStr">
+        <is>
+          <t>Walter Himanen</t>
+        </is>
+      </c>
+      <c r="X229" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y229" s="2" t="inlineStr"/>
+      <c r="Z229" s="2" t="inlineStr"/>
+      <c r="AA229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/walterhimanen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>Diamond Beverages Oy</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>Diamond Beverages Oy</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>23099</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>Vantaa</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>8a Äyritie</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>01510</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>https://diamondbeverages.fi</t>
+        </is>
+      </c>
+      <c r="J230" s="2" t="inlineStr"/>
+      <c r="K230" s="2" t="inlineStr"/>
+      <c r="L230" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M230" s="2" t="inlineStr"/>
+      <c r="N230" s="2" t="inlineStr">
+        <is>
+          <t>diamondbeer@diamondbeverages.fi</t>
+        </is>
+      </c>
+      <c r="O230" s="2" t="inlineStr">
+        <is>
+          <t>+358 10 2310801</t>
+        </is>
+      </c>
+      <c r="P230" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q230" s="2" t="inlineStr">
+        <is>
+          <t>14546792</t>
+        </is>
+      </c>
+      <c r="R230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/diamond-beverages-oy</t>
+        </is>
+      </c>
+      <c r="S230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DiamondBeverages/</t>
+        </is>
+      </c>
+      <c r="T230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/diamondbeverages</t>
+        </is>
+      </c>
+      <c r="U230" s="2" t="inlineStr"/>
+      <c r="V230" s="2" t="inlineStr"/>
+      <c r="W230" s="2" t="inlineStr">
+        <is>
+          <t>Henna Parkkila</t>
+        </is>
+      </c>
+      <c r="X230" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager &amp; Marketing Specialist</t>
+        </is>
+      </c>
+      <c r="Y230" s="2" t="inlineStr"/>
+      <c r="Z230" s="2" t="inlineStr"/>
+      <c r="AA230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hennaparkkila/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Finland.xlsx
+++ b/BWI/bestwine_output/bestwine_Finland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA230"/>
+  <dimension ref="A1:AA248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -26799,6 +26799,1952 @@
         </is>
       </c>
     </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J231" s="2" t="inlineStr"/>
+      <c r="K231" s="2" t="inlineStr"/>
+      <c r="L231" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M231" s="2" t="inlineStr"/>
+      <c r="N231" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O231" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P231" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q231" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U231" s="2" t="inlineStr"/>
+      <c r="V231" s="2" t="inlineStr"/>
+      <c r="W231" s="2" t="inlineStr">
+        <is>
+          <t>Emmi Leinonen</t>
+        </is>
+      </c>
+      <c r="X231" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager Spirits</t>
+        </is>
+      </c>
+      <c r="Y231" s="2" t="inlineStr"/>
+      <c r="Z231" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/emmi-leinonen-1690837b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J232" s="2" t="inlineStr"/>
+      <c r="K232" s="2" t="inlineStr"/>
+      <c r="L232" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M232" s="2" t="inlineStr"/>
+      <c r="N232" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O232" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P232" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q232" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U232" s="2" t="inlineStr"/>
+      <c r="V232" s="2" t="inlineStr"/>
+      <c r="W232" s="2" t="inlineStr">
+        <is>
+          <t>Andrei Cioanca</t>
+        </is>
+      </c>
+      <c r="X232" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager Spirits</t>
+        </is>
+      </c>
+      <c r="Y232" s="2" t="inlineStr"/>
+      <c r="Z232" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andreicioanca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J233" s="2" t="inlineStr"/>
+      <c r="K233" s="2" t="inlineStr"/>
+      <c r="L233" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M233" s="2" t="inlineStr"/>
+      <c r="N233" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O233" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P233" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q233" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U233" s="2" t="inlineStr"/>
+      <c r="V233" s="2" t="inlineStr"/>
+      <c r="W233" s="2" t="inlineStr">
+        <is>
+          <t>Sanna Jäppinen</t>
+        </is>
+      </c>
+      <c r="X233" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager Wines</t>
+        </is>
+      </c>
+      <c r="Y233" s="2" t="inlineStr"/>
+      <c r="Z233" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sanna-j%C3%A4ppinen-07988019/</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J234" s="2" t="inlineStr"/>
+      <c r="K234" s="2" t="inlineStr"/>
+      <c r="L234" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M234" s="2" t="inlineStr"/>
+      <c r="N234" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O234" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P234" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q234" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U234" s="2" t="inlineStr"/>
+      <c r="V234" s="2" t="inlineStr"/>
+      <c r="W234" s="2" t="inlineStr">
+        <is>
+          <t>Joakim Löfström</t>
+        </is>
+      </c>
+      <c r="X234" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y234" s="2" t="inlineStr"/>
+      <c r="Z234" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/joakim-l%C3%B6fstr%C3%B6m-737232/</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J235" s="2" t="inlineStr"/>
+      <c r="K235" s="2" t="inlineStr"/>
+      <c r="L235" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M235" s="2" t="inlineStr"/>
+      <c r="N235" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O235" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P235" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q235" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R235" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S235" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T235" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U235" s="2" t="inlineStr"/>
+      <c r="V235" s="2" t="inlineStr"/>
+      <c r="W235" s="2" t="inlineStr">
+        <is>
+          <t>Timo Laurila</t>
+        </is>
+      </c>
+      <c r="X235" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Director</t>
+        </is>
+      </c>
+      <c r="Y235" s="2" t="inlineStr"/>
+      <c r="Z235" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA235" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/timo-laurila-947078a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J236" s="2" t="inlineStr"/>
+      <c r="K236" s="2" t="inlineStr"/>
+      <c r="L236" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M236" s="2" t="inlineStr"/>
+      <c r="N236" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O236" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P236" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q236" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R236" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S236" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T236" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U236" s="2" t="inlineStr"/>
+      <c r="V236" s="2" t="inlineStr"/>
+      <c r="W236" s="2" t="inlineStr">
+        <is>
+          <t>Joni Granath</t>
+        </is>
+      </c>
+      <c r="X236" s="2" t="inlineStr">
+        <is>
+          <t>Head of On-trade</t>
+        </is>
+      </c>
+      <c r="Y236" s="2" t="inlineStr"/>
+      <c r="Z236" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA236" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/joni-granath/</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J237" s="2" t="inlineStr"/>
+      <c r="K237" s="2" t="inlineStr"/>
+      <c r="L237" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M237" s="2" t="inlineStr"/>
+      <c r="N237" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O237" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P237" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q237" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U237" s="2" t="inlineStr"/>
+      <c r="V237" s="2" t="inlineStr"/>
+      <c r="W237" s="2" t="inlineStr">
+        <is>
+          <t>Kiira Signore</t>
+        </is>
+      </c>
+      <c r="X237" s="2" t="inlineStr">
+        <is>
+          <t>Logistics Coordinator</t>
+        </is>
+      </c>
+      <c r="Y237" s="2" t="inlineStr"/>
+      <c r="Z237" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kiira-signore-31a1a8b6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J238" s="2" t="inlineStr"/>
+      <c r="K238" s="2" t="inlineStr"/>
+      <c r="L238" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M238" s="2" t="inlineStr"/>
+      <c r="N238" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O238" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P238" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q238" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U238" s="2" t="inlineStr"/>
+      <c r="V238" s="2" t="inlineStr"/>
+      <c r="W238" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Jones</t>
+        </is>
+      </c>
+      <c r="X238" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y238" s="2" t="inlineStr"/>
+      <c r="Z238" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patrick-jones-162a875/</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J239" s="2" t="inlineStr"/>
+      <c r="K239" s="2" t="inlineStr"/>
+      <c r="L239" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M239" s="2" t="inlineStr"/>
+      <c r="N239" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O239" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P239" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q239" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R239" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S239" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T239" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U239" s="2" t="inlineStr"/>
+      <c r="V239" s="2" t="inlineStr"/>
+      <c r="W239" s="2" t="inlineStr">
+        <is>
+          <t>Hilla Eerikäinen</t>
+        </is>
+      </c>
+      <c r="X239" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Manager Wines</t>
+        </is>
+      </c>
+      <c r="Y239" s="2" t="inlineStr"/>
+      <c r="Z239" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA239" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hilla-eerik%C3%A4inen-22500985/</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J240" s="2" t="inlineStr"/>
+      <c r="K240" s="2" t="inlineStr"/>
+      <c r="L240" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M240" s="2" t="inlineStr"/>
+      <c r="N240" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O240" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P240" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q240" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U240" s="2" t="inlineStr"/>
+      <c r="V240" s="2" t="inlineStr"/>
+      <c r="W240" s="2" t="inlineStr">
+        <is>
+          <t>Tiina Tuomainen</t>
+        </is>
+      </c>
+      <c r="X240" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager Wines</t>
+        </is>
+      </c>
+      <c r="Y240" s="2" t="inlineStr"/>
+      <c r="Z240" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tiina-tuomainen-b073a486/</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J241" s="2" t="inlineStr"/>
+      <c r="K241" s="2" t="inlineStr"/>
+      <c r="L241" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M241" s="2" t="inlineStr"/>
+      <c r="N241" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O241" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P241" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q241" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R241" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S241" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T241" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U241" s="2" t="inlineStr"/>
+      <c r="V241" s="2" t="inlineStr"/>
+      <c r="W241" s="2" t="inlineStr">
+        <is>
+          <t>Timo Vainonen</t>
+        </is>
+      </c>
+      <c r="X241" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager Wines</t>
+        </is>
+      </c>
+      <c r="Y241" s="2" t="inlineStr"/>
+      <c r="Z241" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA241" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/timo-vainonen-348b0521/</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J242" s="2" t="inlineStr"/>
+      <c r="K242" s="2" t="inlineStr"/>
+      <c r="L242" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M242" s="2" t="inlineStr"/>
+      <c r="N242" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O242" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P242" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q242" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U242" s="2" t="inlineStr"/>
+      <c r="V242" s="2" t="inlineStr"/>
+      <c r="W242" s="2" t="inlineStr">
+        <is>
+          <t>Kalle Sukanen</t>
+        </is>
+      </c>
+      <c r="X242" s="2" t="inlineStr">
+        <is>
+          <t>Senior Brand Manager Spirits</t>
+        </is>
+      </c>
+      <c r="Y242" s="2" t="inlineStr"/>
+      <c r="Z242" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kalle-sukanen-33715a11/</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Oy Winital S.p.a.</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>Oy Winital S.p.a.</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>4073</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>2 Korkeavuorenkatu</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>00140</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>http://winital.fi</t>
+        </is>
+      </c>
+      <c r="J243" s="2" t="inlineStr"/>
+      <c r="K243" s="2" t="inlineStr"/>
+      <c r="L243" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M243" s="2" t="inlineStr"/>
+      <c r="N243" s="2" t="inlineStr">
+        <is>
+          <t>winital@yahoo.com</t>
+        </is>
+      </c>
+      <c r="O243" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 68424840</t>
+        </is>
+      </c>
+      <c r="P243" s="2" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="Q243" s="2" t="inlineStr">
+        <is>
+          <t>09460388</t>
+        </is>
+      </c>
+      <c r="R243" s="2" t="inlineStr"/>
+      <c r="S243" s="2" t="inlineStr"/>
+      <c r="T243" s="2" t="inlineStr"/>
+      <c r="U243" s="2" t="inlineStr"/>
+      <c r="V243" s="2" t="inlineStr"/>
+      <c r="W243" s="2" t="inlineStr">
+        <is>
+          <t>Petri Viglione</t>
+        </is>
+      </c>
+      <c r="X243" s="2" t="inlineStr">
+        <is>
+          <t>Wine Importer</t>
+        </is>
+      </c>
+      <c r="Y243" s="2" t="inlineStr"/>
+      <c r="Z243" s="2" t="inlineStr"/>
+      <c r="AA243" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/petri-viglione-45b1751b8/?originalSubdomain=fi</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>Cisa Drinks Oy</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>Cisa Drinks Oy</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>4020</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>Espoo</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>15 Kavallinmäki</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>02710</t>
+        </is>
+      </c>
+      <c r="I244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cisa.fi</t>
+        </is>
+      </c>
+      <c r="J244" s="2" t="inlineStr"/>
+      <c r="K244" s="2" t="inlineStr"/>
+      <c r="L244" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M244" s="2" t="inlineStr"/>
+      <c r="N244" s="2" t="inlineStr">
+        <is>
+          <t>info@cisa.fi</t>
+        </is>
+      </c>
+      <c r="O244" s="2" t="inlineStr"/>
+      <c r="P244" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q244" s="2" t="inlineStr">
+        <is>
+          <t>18254850</t>
+        </is>
+      </c>
+      <c r="R244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cisa-drinks-oy/</t>
+        </is>
+      </c>
+      <c r="S244" s="2" t="inlineStr"/>
+      <c r="T244" s="2" t="inlineStr"/>
+      <c r="U244" s="2" t="inlineStr"/>
+      <c r="V244" s="2" t="inlineStr"/>
+      <c r="W244" s="2" t="inlineStr">
+        <is>
+          <t>Risto Suomio</t>
+        </is>
+      </c>
+      <c r="X244" s="2" t="inlineStr">
+        <is>
+          <t>Partner, Purchasing</t>
+        </is>
+      </c>
+      <c r="Y244" s="2" t="inlineStr"/>
+      <c r="Z244" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/risto-suomio-2366702/</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>Cisa Drinks Oy</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>Cisa Drinks Oy</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>4020</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>Espoo</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>15 Kavallinmäki</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>02710</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cisa.fi</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="inlineStr"/>
+      <c r="K245" s="2" t="inlineStr"/>
+      <c r="L245" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M245" s="2" t="inlineStr"/>
+      <c r="N245" s="2" t="inlineStr">
+        <is>
+          <t>info@cisa.fi</t>
+        </is>
+      </c>
+      <c r="O245" s="2" t="inlineStr"/>
+      <c r="P245" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q245" s="2" t="inlineStr">
+        <is>
+          <t>18254850</t>
+        </is>
+      </c>
+      <c r="R245" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cisa-drinks-oy/</t>
+        </is>
+      </c>
+      <c r="S245" s="2" t="inlineStr"/>
+      <c r="T245" s="2" t="inlineStr"/>
+      <c r="U245" s="2" t="inlineStr"/>
+      <c r="V245" s="2" t="inlineStr"/>
+      <c r="W245" s="2" t="inlineStr">
+        <is>
+          <t>Toni Vaskivuo</t>
+        </is>
+      </c>
+      <c r="X245" s="2" t="inlineStr">
+        <is>
+          <t>Logistics Controller, Buyer</t>
+        </is>
+      </c>
+      <c r="Y245" s="2" t="inlineStr"/>
+      <c r="Z245" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA245" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/toni-vaskivuo-604727a4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>Wineworld Finland Oy</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>Wineworld Finland Oy</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>35602</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>1 Kaapeliaukio</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>00180</t>
+        </is>
+      </c>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>https://wineworld.fi</t>
+        </is>
+      </c>
+      <c r="J246" s="2" t="inlineStr"/>
+      <c r="K246" s="2" t="inlineStr"/>
+      <c r="L246" s="2" t="inlineStr"/>
+      <c r="M246" s="2" t="inlineStr"/>
+      <c r="N246" s="2" t="inlineStr">
+        <is>
+          <t>info@wineworld.fi</t>
+        </is>
+      </c>
+      <c r="O246" s="2" t="inlineStr"/>
+      <c r="P246" s="2" t="inlineStr"/>
+      <c r="Q246" s="2" t="inlineStr"/>
+      <c r="R246" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wineworld-finland/</t>
+        </is>
+      </c>
+      <c r="S246" s="2" t="inlineStr"/>
+      <c r="T246" s="2" t="inlineStr"/>
+      <c r="U246" s="2" t="inlineStr"/>
+      <c r="V246" s="2" t="inlineStr"/>
+      <c r="W246" s="2" t="inlineStr"/>
+      <c r="X246" s="2" t="inlineStr"/>
+      <c r="Y246" s="2" t="inlineStr"/>
+      <c r="Z246" s="2" t="inlineStr"/>
+      <c r="AA246" s="2" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>Diamond Beverages Oy</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>Diamond Beverages Oy</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>23099</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>Vantaa</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>8a Äyritie</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>01510</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>https://diamondbeverages.fi</t>
+        </is>
+      </c>
+      <c r="J247" s="2" t="inlineStr"/>
+      <c r="K247" s="2" t="inlineStr"/>
+      <c r="L247" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M247" s="2" t="inlineStr"/>
+      <c r="N247" s="2" t="inlineStr">
+        <is>
+          <t>diamondbeer@diamondbeverages.fi</t>
+        </is>
+      </c>
+      <c r="O247" s="2" t="inlineStr">
+        <is>
+          <t>+358 10 2310801</t>
+        </is>
+      </c>
+      <c r="P247" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q247" s="2" t="inlineStr">
+        <is>
+          <t>14546792</t>
+        </is>
+      </c>
+      <c r="R247" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/diamond-beverages-oy</t>
+        </is>
+      </c>
+      <c r="S247" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DiamondBeverages/</t>
+        </is>
+      </c>
+      <c r="T247" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/diamondbeverages</t>
+        </is>
+      </c>
+      <c r="U247" s="2" t="inlineStr"/>
+      <c r="V247" s="2" t="inlineStr"/>
+      <c r="W247" s="2" t="inlineStr">
+        <is>
+          <t>Walter Himanen</t>
+        </is>
+      </c>
+      <c r="X247" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y247" s="2" t="inlineStr"/>
+      <c r="Z247" s="2" t="inlineStr"/>
+      <c r="AA247" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/walterhimanen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>Diamond Beverages Oy</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>Diamond Beverages Oy</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>23099</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>Vantaa</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>8a Äyritie</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>01510</t>
+        </is>
+      </c>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>https://diamondbeverages.fi</t>
+        </is>
+      </c>
+      <c r="J248" s="2" t="inlineStr"/>
+      <c r="K248" s="2" t="inlineStr"/>
+      <c r="L248" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M248" s="2" t="inlineStr"/>
+      <c r="N248" s="2" t="inlineStr">
+        <is>
+          <t>diamondbeer@diamondbeverages.fi</t>
+        </is>
+      </c>
+      <c r="O248" s="2" t="inlineStr">
+        <is>
+          <t>+358 10 2310801</t>
+        </is>
+      </c>
+      <c r="P248" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q248" s="2" t="inlineStr">
+        <is>
+          <t>14546792</t>
+        </is>
+      </c>
+      <c r="R248" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/diamond-beverages-oy</t>
+        </is>
+      </c>
+      <c r="S248" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DiamondBeverages/</t>
+        </is>
+      </c>
+      <c r="T248" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/diamondbeverages</t>
+        </is>
+      </c>
+      <c r="U248" s="2" t="inlineStr"/>
+      <c r="V248" s="2" t="inlineStr"/>
+      <c r="W248" s="2" t="inlineStr">
+        <is>
+          <t>Henna Parkkila</t>
+        </is>
+      </c>
+      <c r="X248" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager &amp; Marketing Specialist</t>
+        </is>
+      </c>
+      <c r="Y248" s="2" t="inlineStr"/>
+      <c r="Z248" s="2" t="inlineStr"/>
+      <c r="AA248" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hennaparkkila/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Finland.xlsx
+++ b/BWI/bestwine_output/bestwine_Finland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA248"/>
+  <dimension ref="A1:AA266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -28745,6 +28745,1952 @@
         </is>
       </c>
     </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J249" s="2" t="inlineStr"/>
+      <c r="K249" s="2" t="inlineStr"/>
+      <c r="L249" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M249" s="2" t="inlineStr"/>
+      <c r="N249" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O249" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P249" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q249" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U249" s="2" t="inlineStr"/>
+      <c r="V249" s="2" t="inlineStr"/>
+      <c r="W249" s="2" t="inlineStr">
+        <is>
+          <t>Emmi Leinonen</t>
+        </is>
+      </c>
+      <c r="X249" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager Spirits</t>
+        </is>
+      </c>
+      <c r="Y249" s="2" t="inlineStr"/>
+      <c r="Z249" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/emmi-leinonen-1690837b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J250" s="2" t="inlineStr"/>
+      <c r="K250" s="2" t="inlineStr"/>
+      <c r="L250" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M250" s="2" t="inlineStr"/>
+      <c r="N250" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O250" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P250" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q250" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U250" s="2" t="inlineStr"/>
+      <c r="V250" s="2" t="inlineStr"/>
+      <c r="W250" s="2" t="inlineStr">
+        <is>
+          <t>Andrei Cioanca</t>
+        </is>
+      </c>
+      <c r="X250" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager Spirits</t>
+        </is>
+      </c>
+      <c r="Y250" s="2" t="inlineStr"/>
+      <c r="Z250" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andreicioanca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J251" s="2" t="inlineStr"/>
+      <c r="K251" s="2" t="inlineStr"/>
+      <c r="L251" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M251" s="2" t="inlineStr"/>
+      <c r="N251" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O251" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P251" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q251" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U251" s="2" t="inlineStr"/>
+      <c r="V251" s="2" t="inlineStr"/>
+      <c r="W251" s="2" t="inlineStr">
+        <is>
+          <t>Sanna Jäppinen</t>
+        </is>
+      </c>
+      <c r="X251" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager Wines</t>
+        </is>
+      </c>
+      <c r="Y251" s="2" t="inlineStr"/>
+      <c r="Z251" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sanna-j%C3%A4ppinen-07988019/</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J252" s="2" t="inlineStr"/>
+      <c r="K252" s="2" t="inlineStr"/>
+      <c r="L252" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M252" s="2" t="inlineStr"/>
+      <c r="N252" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O252" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P252" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q252" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U252" s="2" t="inlineStr"/>
+      <c r="V252" s="2" t="inlineStr"/>
+      <c r="W252" s="2" t="inlineStr">
+        <is>
+          <t>Joakim Löfström</t>
+        </is>
+      </c>
+      <c r="X252" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y252" s="2" t="inlineStr"/>
+      <c r="Z252" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/joakim-l%C3%B6fstr%C3%B6m-737232/</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J253" s="2" t="inlineStr"/>
+      <c r="K253" s="2" t="inlineStr"/>
+      <c r="L253" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M253" s="2" t="inlineStr"/>
+      <c r="N253" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O253" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P253" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q253" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R253" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S253" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T253" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U253" s="2" t="inlineStr"/>
+      <c r="V253" s="2" t="inlineStr"/>
+      <c r="W253" s="2" t="inlineStr">
+        <is>
+          <t>Timo Laurila</t>
+        </is>
+      </c>
+      <c r="X253" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Director</t>
+        </is>
+      </c>
+      <c r="Y253" s="2" t="inlineStr"/>
+      <c r="Z253" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA253" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/timo-laurila-947078a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J254" s="2" t="inlineStr"/>
+      <c r="K254" s="2" t="inlineStr"/>
+      <c r="L254" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M254" s="2" t="inlineStr"/>
+      <c r="N254" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O254" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P254" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q254" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R254" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S254" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T254" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U254" s="2" t="inlineStr"/>
+      <c r="V254" s="2" t="inlineStr"/>
+      <c r="W254" s="2" t="inlineStr">
+        <is>
+          <t>Joni Granath</t>
+        </is>
+      </c>
+      <c r="X254" s="2" t="inlineStr">
+        <is>
+          <t>Head of On-trade</t>
+        </is>
+      </c>
+      <c r="Y254" s="2" t="inlineStr"/>
+      <c r="Z254" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA254" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/joni-granath/</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I255" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J255" s="2" t="inlineStr"/>
+      <c r="K255" s="2" t="inlineStr"/>
+      <c r="L255" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M255" s="2" t="inlineStr"/>
+      <c r="N255" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O255" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P255" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q255" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R255" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S255" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T255" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U255" s="2" t="inlineStr"/>
+      <c r="V255" s="2" t="inlineStr"/>
+      <c r="W255" s="2" t="inlineStr">
+        <is>
+          <t>Kiira Signore</t>
+        </is>
+      </c>
+      <c r="X255" s="2" t="inlineStr">
+        <is>
+          <t>Logistics Coordinator</t>
+        </is>
+      </c>
+      <c r="Y255" s="2" t="inlineStr"/>
+      <c r="Z255" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA255" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kiira-signore-31a1a8b6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J256" s="2" t="inlineStr"/>
+      <c r="K256" s="2" t="inlineStr"/>
+      <c r="L256" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M256" s="2" t="inlineStr"/>
+      <c r="N256" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O256" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P256" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q256" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R256" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S256" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T256" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U256" s="2" t="inlineStr"/>
+      <c r="V256" s="2" t="inlineStr"/>
+      <c r="W256" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Jones</t>
+        </is>
+      </c>
+      <c r="X256" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y256" s="2" t="inlineStr"/>
+      <c r="Z256" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA256" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patrick-jones-162a875/</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I257" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J257" s="2" t="inlineStr"/>
+      <c r="K257" s="2" t="inlineStr"/>
+      <c r="L257" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M257" s="2" t="inlineStr"/>
+      <c r="N257" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O257" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P257" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q257" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R257" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S257" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T257" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U257" s="2" t="inlineStr"/>
+      <c r="V257" s="2" t="inlineStr"/>
+      <c r="W257" s="2" t="inlineStr">
+        <is>
+          <t>Hilla Eerikäinen</t>
+        </is>
+      </c>
+      <c r="X257" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Manager Wines</t>
+        </is>
+      </c>
+      <c r="Y257" s="2" t="inlineStr"/>
+      <c r="Z257" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA257" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hilla-eerik%C3%A4inen-22500985/</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J258" s="2" t="inlineStr"/>
+      <c r="K258" s="2" t="inlineStr"/>
+      <c r="L258" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M258" s="2" t="inlineStr"/>
+      <c r="N258" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O258" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P258" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q258" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U258" s="2" t="inlineStr"/>
+      <c r="V258" s="2" t="inlineStr"/>
+      <c r="W258" s="2" t="inlineStr">
+        <is>
+          <t>Tiina Tuomainen</t>
+        </is>
+      </c>
+      <c r="X258" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager Wines</t>
+        </is>
+      </c>
+      <c r="Y258" s="2" t="inlineStr"/>
+      <c r="Z258" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tiina-tuomainen-b073a486/</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J259" s="2" t="inlineStr"/>
+      <c r="K259" s="2" t="inlineStr"/>
+      <c r="L259" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M259" s="2" t="inlineStr"/>
+      <c r="N259" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O259" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P259" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q259" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U259" s="2" t="inlineStr"/>
+      <c r="V259" s="2" t="inlineStr"/>
+      <c r="W259" s="2" t="inlineStr">
+        <is>
+          <t>Timo Vainonen</t>
+        </is>
+      </c>
+      <c r="X259" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager Wines</t>
+        </is>
+      </c>
+      <c r="Y259" s="2" t="inlineStr"/>
+      <c r="Z259" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/timo-vainonen-348b0521/</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J260" s="2" t="inlineStr"/>
+      <c r="K260" s="2" t="inlineStr"/>
+      <c r="L260" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M260" s="2" t="inlineStr"/>
+      <c r="N260" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O260" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P260" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q260" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U260" s="2" t="inlineStr"/>
+      <c r="V260" s="2" t="inlineStr"/>
+      <c r="W260" s="2" t="inlineStr">
+        <is>
+          <t>Kalle Sukanen</t>
+        </is>
+      </c>
+      <c r="X260" s="2" t="inlineStr">
+        <is>
+          <t>Senior Brand Manager Spirits</t>
+        </is>
+      </c>
+      <c r="Y260" s="2" t="inlineStr"/>
+      <c r="Z260" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA260" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kalle-sukanen-33715a11/</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>Oy Winital S.p.a.</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>Oy Winital S.p.a.</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>4073</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>2 Korkeavuorenkatu</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>00140</t>
+        </is>
+      </c>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>http://winital.fi</t>
+        </is>
+      </c>
+      <c r="J261" s="2" t="inlineStr"/>
+      <c r="K261" s="2" t="inlineStr"/>
+      <c r="L261" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M261" s="2" t="inlineStr"/>
+      <c r="N261" s="2" t="inlineStr">
+        <is>
+          <t>winital@yahoo.com</t>
+        </is>
+      </c>
+      <c r="O261" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 68424840</t>
+        </is>
+      </c>
+      <c r="P261" s="2" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="Q261" s="2" t="inlineStr">
+        <is>
+          <t>09460388</t>
+        </is>
+      </c>
+      <c r="R261" s="2" t="inlineStr"/>
+      <c r="S261" s="2" t="inlineStr"/>
+      <c r="T261" s="2" t="inlineStr"/>
+      <c r="U261" s="2" t="inlineStr"/>
+      <c r="V261" s="2" t="inlineStr"/>
+      <c r="W261" s="2" t="inlineStr">
+        <is>
+          <t>Petri Viglione</t>
+        </is>
+      </c>
+      <c r="X261" s="2" t="inlineStr">
+        <is>
+          <t>Wine Importer</t>
+        </is>
+      </c>
+      <c r="Y261" s="2" t="inlineStr"/>
+      <c r="Z261" s="2" t="inlineStr"/>
+      <c r="AA261" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/petri-viglione-45b1751b8/?originalSubdomain=fi</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>Cisa Drinks Oy</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>Cisa Drinks Oy</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>4020</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>Espoo</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>15 Kavallinmäki</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>02710</t>
+        </is>
+      </c>
+      <c r="I262" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cisa.fi</t>
+        </is>
+      </c>
+      <c r="J262" s="2" t="inlineStr"/>
+      <c r="K262" s="2" t="inlineStr"/>
+      <c r="L262" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M262" s="2" t="inlineStr"/>
+      <c r="N262" s="2" t="inlineStr">
+        <is>
+          <t>info@cisa.fi</t>
+        </is>
+      </c>
+      <c r="O262" s="2" t="inlineStr"/>
+      <c r="P262" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q262" s="2" t="inlineStr">
+        <is>
+          <t>18254850</t>
+        </is>
+      </c>
+      <c r="R262" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cisa-drinks-oy/</t>
+        </is>
+      </c>
+      <c r="S262" s="2" t="inlineStr"/>
+      <c r="T262" s="2" t="inlineStr"/>
+      <c r="U262" s="2" t="inlineStr"/>
+      <c r="V262" s="2" t="inlineStr"/>
+      <c r="W262" s="2" t="inlineStr">
+        <is>
+          <t>Risto Suomio</t>
+        </is>
+      </c>
+      <c r="X262" s="2" t="inlineStr">
+        <is>
+          <t>Partner, Purchasing</t>
+        </is>
+      </c>
+      <c r="Y262" s="2" t="inlineStr"/>
+      <c r="Z262" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA262" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/risto-suomio-2366702/</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>Cisa Drinks Oy</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>Cisa Drinks Oy</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>4020</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>Espoo</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>15 Kavallinmäki</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>02710</t>
+        </is>
+      </c>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cisa.fi</t>
+        </is>
+      </c>
+      <c r="J263" s="2" t="inlineStr"/>
+      <c r="K263" s="2" t="inlineStr"/>
+      <c r="L263" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M263" s="2" t="inlineStr"/>
+      <c r="N263" s="2" t="inlineStr">
+        <is>
+          <t>info@cisa.fi</t>
+        </is>
+      </c>
+      <c r="O263" s="2" t="inlineStr"/>
+      <c r="P263" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q263" s="2" t="inlineStr">
+        <is>
+          <t>18254850</t>
+        </is>
+      </c>
+      <c r="R263" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cisa-drinks-oy/</t>
+        </is>
+      </c>
+      <c r="S263" s="2" t="inlineStr"/>
+      <c r="T263" s="2" t="inlineStr"/>
+      <c r="U263" s="2" t="inlineStr"/>
+      <c r="V263" s="2" t="inlineStr"/>
+      <c r="W263" s="2" t="inlineStr">
+        <is>
+          <t>Toni Vaskivuo</t>
+        </is>
+      </c>
+      <c r="X263" s="2" t="inlineStr">
+        <is>
+          <t>Logistics Controller, Buyer</t>
+        </is>
+      </c>
+      <c r="Y263" s="2" t="inlineStr"/>
+      <c r="Z263" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA263" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/toni-vaskivuo-604727a4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>Wineworld Finland Oy</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>Wineworld Finland Oy</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>35602</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>1 Kaapeliaukio</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>00180</t>
+        </is>
+      </c>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>https://wineworld.fi</t>
+        </is>
+      </c>
+      <c r="J264" s="2" t="inlineStr"/>
+      <c r="K264" s="2" t="inlineStr"/>
+      <c r="L264" s="2" t="inlineStr"/>
+      <c r="M264" s="2" t="inlineStr"/>
+      <c r="N264" s="2" t="inlineStr">
+        <is>
+          <t>info@wineworld.fi</t>
+        </is>
+      </c>
+      <c r="O264" s="2" t="inlineStr"/>
+      <c r="P264" s="2" t="inlineStr"/>
+      <c r="Q264" s="2" t="inlineStr"/>
+      <c r="R264" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wineworld-finland/</t>
+        </is>
+      </c>
+      <c r="S264" s="2" t="inlineStr"/>
+      <c r="T264" s="2" t="inlineStr"/>
+      <c r="U264" s="2" t="inlineStr"/>
+      <c r="V264" s="2" t="inlineStr"/>
+      <c r="W264" s="2" t="inlineStr"/>
+      <c r="X264" s="2" t="inlineStr"/>
+      <c r="Y264" s="2" t="inlineStr"/>
+      <c r="Z264" s="2" t="inlineStr"/>
+      <c r="AA264" s="2" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>Diamond Beverages Oy</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>Diamond Beverages Oy</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>23099</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>Vantaa</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>8a Äyritie</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>01510</t>
+        </is>
+      </c>
+      <c r="I265" s="2" t="inlineStr">
+        <is>
+          <t>https://diamondbeverages.fi</t>
+        </is>
+      </c>
+      <c r="J265" s="2" t="inlineStr"/>
+      <c r="K265" s="2" t="inlineStr"/>
+      <c r="L265" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M265" s="2" t="inlineStr"/>
+      <c r="N265" s="2" t="inlineStr">
+        <is>
+          <t>diamondbeer@diamondbeverages.fi</t>
+        </is>
+      </c>
+      <c r="O265" s="2" t="inlineStr">
+        <is>
+          <t>+358 10 2310801</t>
+        </is>
+      </c>
+      <c r="P265" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q265" s="2" t="inlineStr">
+        <is>
+          <t>14546792</t>
+        </is>
+      </c>
+      <c r="R265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/diamond-beverages-oy</t>
+        </is>
+      </c>
+      <c r="S265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DiamondBeverages/</t>
+        </is>
+      </c>
+      <c r="T265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/diamondbeverages</t>
+        </is>
+      </c>
+      <c r="U265" s="2" t="inlineStr"/>
+      <c r="V265" s="2" t="inlineStr"/>
+      <c r="W265" s="2" t="inlineStr">
+        <is>
+          <t>Walter Himanen</t>
+        </is>
+      </c>
+      <c r="X265" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y265" s="2" t="inlineStr"/>
+      <c r="Z265" s="2" t="inlineStr"/>
+      <c r="AA265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/walterhimanen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>Diamond Beverages Oy</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>Diamond Beverages Oy</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>23099</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>Vantaa</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>8a Äyritie</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>01510</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>https://diamondbeverages.fi</t>
+        </is>
+      </c>
+      <c r="J266" s="2" t="inlineStr"/>
+      <c r="K266" s="2" t="inlineStr"/>
+      <c r="L266" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M266" s="2" t="inlineStr"/>
+      <c r="N266" s="2" t="inlineStr">
+        <is>
+          <t>diamondbeer@diamondbeverages.fi</t>
+        </is>
+      </c>
+      <c r="O266" s="2" t="inlineStr">
+        <is>
+          <t>+358 10 2310801</t>
+        </is>
+      </c>
+      <c r="P266" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q266" s="2" t="inlineStr">
+        <is>
+          <t>14546792</t>
+        </is>
+      </c>
+      <c r="R266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/diamond-beverages-oy</t>
+        </is>
+      </c>
+      <c r="S266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DiamondBeverages/</t>
+        </is>
+      </c>
+      <c r="T266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/diamondbeverages</t>
+        </is>
+      </c>
+      <c r="U266" s="2" t="inlineStr"/>
+      <c r="V266" s="2" t="inlineStr"/>
+      <c r="W266" s="2" t="inlineStr">
+        <is>
+          <t>Henna Parkkila</t>
+        </is>
+      </c>
+      <c r="X266" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager &amp; Marketing Specialist</t>
+        </is>
+      </c>
+      <c r="Y266" s="2" t="inlineStr"/>
+      <c r="Z266" s="2" t="inlineStr"/>
+      <c r="AA266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hennaparkkila/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Finland.xlsx
+++ b/BWI/bestwine_output/bestwine_Finland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA266"/>
+  <dimension ref="A1:AA284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -30691,6 +30691,1952 @@
         </is>
       </c>
     </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J267" s="2" t="inlineStr"/>
+      <c r="K267" s="2" t="inlineStr"/>
+      <c r="L267" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M267" s="2" t="inlineStr"/>
+      <c r="N267" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O267" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P267" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q267" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R267" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S267" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T267" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U267" s="2" t="inlineStr"/>
+      <c r="V267" s="2" t="inlineStr"/>
+      <c r="W267" s="2" t="inlineStr">
+        <is>
+          <t>Emmi Leinonen</t>
+        </is>
+      </c>
+      <c r="X267" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager Spirits</t>
+        </is>
+      </c>
+      <c r="Y267" s="2" t="inlineStr"/>
+      <c r="Z267" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA267" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/emmi-leinonen-1690837b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J268" s="2" t="inlineStr"/>
+      <c r="K268" s="2" t="inlineStr"/>
+      <c r="L268" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M268" s="2" t="inlineStr"/>
+      <c r="N268" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O268" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P268" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q268" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U268" s="2" t="inlineStr"/>
+      <c r="V268" s="2" t="inlineStr"/>
+      <c r="W268" s="2" t="inlineStr">
+        <is>
+          <t>Andrei Cioanca</t>
+        </is>
+      </c>
+      <c r="X268" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager Spirits</t>
+        </is>
+      </c>
+      <c r="Y268" s="2" t="inlineStr"/>
+      <c r="Z268" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andreicioanca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H269" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J269" s="2" t="inlineStr"/>
+      <c r="K269" s="2" t="inlineStr"/>
+      <c r="L269" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M269" s="2" t="inlineStr"/>
+      <c r="N269" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O269" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P269" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q269" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U269" s="2" t="inlineStr"/>
+      <c r="V269" s="2" t="inlineStr"/>
+      <c r="W269" s="2" t="inlineStr">
+        <is>
+          <t>Sanna Jäppinen</t>
+        </is>
+      </c>
+      <c r="X269" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager Wines</t>
+        </is>
+      </c>
+      <c r="Y269" s="2" t="inlineStr"/>
+      <c r="Z269" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA269" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sanna-j%C3%A4ppinen-07988019/</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H270" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J270" s="2" t="inlineStr"/>
+      <c r="K270" s="2" t="inlineStr"/>
+      <c r="L270" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M270" s="2" t="inlineStr"/>
+      <c r="N270" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O270" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P270" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q270" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U270" s="2" t="inlineStr"/>
+      <c r="V270" s="2" t="inlineStr"/>
+      <c r="W270" s="2" t="inlineStr">
+        <is>
+          <t>Joakim Löfström</t>
+        </is>
+      </c>
+      <c r="X270" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y270" s="2" t="inlineStr"/>
+      <c r="Z270" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA270" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/joakim-l%C3%B6fstr%C3%B6m-737232/</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H271" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J271" s="2" t="inlineStr"/>
+      <c r="K271" s="2" t="inlineStr"/>
+      <c r="L271" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M271" s="2" t="inlineStr"/>
+      <c r="N271" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O271" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P271" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q271" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U271" s="2" t="inlineStr"/>
+      <c r="V271" s="2" t="inlineStr"/>
+      <c r="W271" s="2" t="inlineStr">
+        <is>
+          <t>Timo Laurila</t>
+        </is>
+      </c>
+      <c r="X271" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Director</t>
+        </is>
+      </c>
+      <c r="Y271" s="2" t="inlineStr"/>
+      <c r="Z271" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA271" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/timo-laurila-947078a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H272" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J272" s="2" t="inlineStr"/>
+      <c r="K272" s="2" t="inlineStr"/>
+      <c r="L272" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M272" s="2" t="inlineStr"/>
+      <c r="N272" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O272" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P272" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q272" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U272" s="2" t="inlineStr"/>
+      <c r="V272" s="2" t="inlineStr"/>
+      <c r="W272" s="2" t="inlineStr">
+        <is>
+          <t>Joni Granath</t>
+        </is>
+      </c>
+      <c r="X272" s="2" t="inlineStr">
+        <is>
+          <t>Head of On-trade</t>
+        </is>
+      </c>
+      <c r="Y272" s="2" t="inlineStr"/>
+      <c r="Z272" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA272" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/joni-granath/</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H273" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J273" s="2" t="inlineStr"/>
+      <c r="K273" s="2" t="inlineStr"/>
+      <c r="L273" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M273" s="2" t="inlineStr"/>
+      <c r="N273" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O273" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P273" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q273" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U273" s="2" t="inlineStr"/>
+      <c r="V273" s="2" t="inlineStr"/>
+      <c r="W273" s="2" t="inlineStr">
+        <is>
+          <t>Kiira Signore</t>
+        </is>
+      </c>
+      <c r="X273" s="2" t="inlineStr">
+        <is>
+          <t>Logistics Coordinator</t>
+        </is>
+      </c>
+      <c r="Y273" s="2" t="inlineStr"/>
+      <c r="Z273" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA273" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kiira-signore-31a1a8b6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H274" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J274" s="2" t="inlineStr"/>
+      <c r="K274" s="2" t="inlineStr"/>
+      <c r="L274" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M274" s="2" t="inlineStr"/>
+      <c r="N274" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O274" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P274" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q274" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R274" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S274" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T274" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U274" s="2" t="inlineStr"/>
+      <c r="V274" s="2" t="inlineStr"/>
+      <c r="W274" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Jones</t>
+        </is>
+      </c>
+      <c r="X274" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y274" s="2" t="inlineStr"/>
+      <c r="Z274" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA274" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patrick-jones-162a875/</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F275" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H275" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I275" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J275" s="2" t="inlineStr"/>
+      <c r="K275" s="2" t="inlineStr"/>
+      <c r="L275" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M275" s="2" t="inlineStr"/>
+      <c r="N275" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O275" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P275" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q275" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R275" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S275" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T275" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U275" s="2" t="inlineStr"/>
+      <c r="V275" s="2" t="inlineStr"/>
+      <c r="W275" s="2" t="inlineStr">
+        <is>
+          <t>Hilla Eerikäinen</t>
+        </is>
+      </c>
+      <c r="X275" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Manager Wines</t>
+        </is>
+      </c>
+      <c r="Y275" s="2" t="inlineStr"/>
+      <c r="Z275" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA275" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hilla-eerik%C3%A4inen-22500985/</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F276" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H276" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I276" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J276" s="2" t="inlineStr"/>
+      <c r="K276" s="2" t="inlineStr"/>
+      <c r="L276" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M276" s="2" t="inlineStr"/>
+      <c r="N276" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O276" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P276" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q276" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R276" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S276" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T276" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U276" s="2" t="inlineStr"/>
+      <c r="V276" s="2" t="inlineStr"/>
+      <c r="W276" s="2" t="inlineStr">
+        <is>
+          <t>Tiina Tuomainen</t>
+        </is>
+      </c>
+      <c r="X276" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager Wines</t>
+        </is>
+      </c>
+      <c r="Y276" s="2" t="inlineStr"/>
+      <c r="Z276" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA276" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tiina-tuomainen-b073a486/</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F277" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H277" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J277" s="2" t="inlineStr"/>
+      <c r="K277" s="2" t="inlineStr"/>
+      <c r="L277" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M277" s="2" t="inlineStr"/>
+      <c r="N277" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O277" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P277" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q277" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U277" s="2" t="inlineStr"/>
+      <c r="V277" s="2" t="inlineStr"/>
+      <c r="W277" s="2" t="inlineStr">
+        <is>
+          <t>Timo Vainonen</t>
+        </is>
+      </c>
+      <c r="X277" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager Wines</t>
+        </is>
+      </c>
+      <c r="Y277" s="2" t="inlineStr"/>
+      <c r="Z277" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA277" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/timo-vainonen-348b0521/</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F278" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H278" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J278" s="2" t="inlineStr"/>
+      <c r="K278" s="2" t="inlineStr"/>
+      <c r="L278" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M278" s="2" t="inlineStr"/>
+      <c r="N278" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O278" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P278" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q278" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R278" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S278" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T278" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U278" s="2" t="inlineStr"/>
+      <c r="V278" s="2" t="inlineStr"/>
+      <c r="W278" s="2" t="inlineStr">
+        <is>
+          <t>Kalle Sukanen</t>
+        </is>
+      </c>
+      <c r="X278" s="2" t="inlineStr">
+        <is>
+          <t>Senior Brand Manager Spirits</t>
+        </is>
+      </c>
+      <c r="Y278" s="2" t="inlineStr"/>
+      <c r="Z278" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA278" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kalle-sukanen-33715a11/</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>Oy Winital S.p.a.</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>Oy Winital S.p.a.</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>4073</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F279" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>2 Korkeavuorenkatu</t>
+        </is>
+      </c>
+      <c r="H279" s="2" t="inlineStr">
+        <is>
+          <t>00140</t>
+        </is>
+      </c>
+      <c r="I279" s="2" t="inlineStr">
+        <is>
+          <t>http://winital.fi</t>
+        </is>
+      </c>
+      <c r="J279" s="2" t="inlineStr"/>
+      <c r="K279" s="2" t="inlineStr"/>
+      <c r="L279" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M279" s="2" t="inlineStr"/>
+      <c r="N279" s="2" t="inlineStr">
+        <is>
+          <t>winital@yahoo.com</t>
+        </is>
+      </c>
+      <c r="O279" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 68424840</t>
+        </is>
+      </c>
+      <c r="P279" s="2" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="Q279" s="2" t="inlineStr">
+        <is>
+          <t>09460388</t>
+        </is>
+      </c>
+      <c r="R279" s="2" t="inlineStr"/>
+      <c r="S279" s="2" t="inlineStr"/>
+      <c r="T279" s="2" t="inlineStr"/>
+      <c r="U279" s="2" t="inlineStr"/>
+      <c r="V279" s="2" t="inlineStr"/>
+      <c r="W279" s="2" t="inlineStr">
+        <is>
+          <t>Petri Viglione</t>
+        </is>
+      </c>
+      <c r="X279" s="2" t="inlineStr">
+        <is>
+          <t>Wine Importer</t>
+        </is>
+      </c>
+      <c r="Y279" s="2" t="inlineStr"/>
+      <c r="Z279" s="2" t="inlineStr"/>
+      <c r="AA279" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/petri-viglione-45b1751b8/?originalSubdomain=fi</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>Cisa Drinks Oy</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>Cisa Drinks Oy</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="inlineStr">
+        <is>
+          <t>4020</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E280" s="2" t="inlineStr">
+        <is>
+          <t>Espoo</t>
+        </is>
+      </c>
+      <c r="F280" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>15 Kavallinmäki</t>
+        </is>
+      </c>
+      <c r="H280" s="2" t="inlineStr">
+        <is>
+          <t>02710</t>
+        </is>
+      </c>
+      <c r="I280" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cisa.fi</t>
+        </is>
+      </c>
+      <c r="J280" s="2" t="inlineStr"/>
+      <c r="K280" s="2" t="inlineStr"/>
+      <c r="L280" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M280" s="2" t="inlineStr"/>
+      <c r="N280" s="2" t="inlineStr">
+        <is>
+          <t>info@cisa.fi</t>
+        </is>
+      </c>
+      <c r="O280" s="2" t="inlineStr"/>
+      <c r="P280" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q280" s="2" t="inlineStr">
+        <is>
+          <t>18254850</t>
+        </is>
+      </c>
+      <c r="R280" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cisa-drinks-oy/</t>
+        </is>
+      </c>
+      <c r="S280" s="2" t="inlineStr"/>
+      <c r="T280" s="2" t="inlineStr"/>
+      <c r="U280" s="2" t="inlineStr"/>
+      <c r="V280" s="2" t="inlineStr"/>
+      <c r="W280" s="2" t="inlineStr">
+        <is>
+          <t>Risto Suomio</t>
+        </is>
+      </c>
+      <c r="X280" s="2" t="inlineStr">
+        <is>
+          <t>Partner, Purchasing</t>
+        </is>
+      </c>
+      <c r="Y280" s="2" t="inlineStr"/>
+      <c r="Z280" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA280" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/risto-suomio-2366702/</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>Cisa Drinks Oy</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>Cisa Drinks Oy</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>4020</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>Espoo</t>
+        </is>
+      </c>
+      <c r="F281" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>15 Kavallinmäki</t>
+        </is>
+      </c>
+      <c r="H281" s="2" t="inlineStr">
+        <is>
+          <t>02710</t>
+        </is>
+      </c>
+      <c r="I281" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cisa.fi</t>
+        </is>
+      </c>
+      <c r="J281" s="2" t="inlineStr"/>
+      <c r="K281" s="2" t="inlineStr"/>
+      <c r="L281" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M281" s="2" t="inlineStr"/>
+      <c r="N281" s="2" t="inlineStr">
+        <is>
+          <t>info@cisa.fi</t>
+        </is>
+      </c>
+      <c r="O281" s="2" t="inlineStr"/>
+      <c r="P281" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q281" s="2" t="inlineStr">
+        <is>
+          <t>18254850</t>
+        </is>
+      </c>
+      <c r="R281" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cisa-drinks-oy/</t>
+        </is>
+      </c>
+      <c r="S281" s="2" t="inlineStr"/>
+      <c r="T281" s="2" t="inlineStr"/>
+      <c r="U281" s="2" t="inlineStr"/>
+      <c r="V281" s="2" t="inlineStr"/>
+      <c r="W281" s="2" t="inlineStr">
+        <is>
+          <t>Toni Vaskivuo</t>
+        </is>
+      </c>
+      <c r="X281" s="2" t="inlineStr">
+        <is>
+          <t>Logistics Controller, Buyer</t>
+        </is>
+      </c>
+      <c r="Y281" s="2" t="inlineStr"/>
+      <c r="Z281" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA281" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/toni-vaskivuo-604727a4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>Wineworld Finland Oy</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>Wineworld Finland Oy</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>35602</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>1 Kaapeliaukio</t>
+        </is>
+      </c>
+      <c r="H282" s="2" t="inlineStr">
+        <is>
+          <t>00180</t>
+        </is>
+      </c>
+      <c r="I282" s="2" t="inlineStr">
+        <is>
+          <t>https://wineworld.fi</t>
+        </is>
+      </c>
+      <c r="J282" s="2" t="inlineStr"/>
+      <c r="K282" s="2" t="inlineStr"/>
+      <c r="L282" s="2" t="inlineStr"/>
+      <c r="M282" s="2" t="inlineStr"/>
+      <c r="N282" s="2" t="inlineStr">
+        <is>
+          <t>info@wineworld.fi</t>
+        </is>
+      </c>
+      <c r="O282" s="2" t="inlineStr"/>
+      <c r="P282" s="2" t="inlineStr"/>
+      <c r="Q282" s="2" t="inlineStr"/>
+      <c r="R282" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wineworld-finland/</t>
+        </is>
+      </c>
+      <c r="S282" s="2" t="inlineStr"/>
+      <c r="T282" s="2" t="inlineStr"/>
+      <c r="U282" s="2" t="inlineStr"/>
+      <c r="V282" s="2" t="inlineStr"/>
+      <c r="W282" s="2" t="inlineStr"/>
+      <c r="X282" s="2" t="inlineStr"/>
+      <c r="Y282" s="2" t="inlineStr"/>
+      <c r="Z282" s="2" t="inlineStr"/>
+      <c r="AA282" s="2" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>Diamond Beverages Oy</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>Diamond Beverages Oy</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>23099</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>Vantaa</t>
+        </is>
+      </c>
+      <c r="F283" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>8a Äyritie</t>
+        </is>
+      </c>
+      <c r="H283" s="2" t="inlineStr">
+        <is>
+          <t>01510</t>
+        </is>
+      </c>
+      <c r="I283" s="2" t="inlineStr">
+        <is>
+          <t>https://diamondbeverages.fi</t>
+        </is>
+      </c>
+      <c r="J283" s="2" t="inlineStr"/>
+      <c r="K283" s="2" t="inlineStr"/>
+      <c r="L283" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M283" s="2" t="inlineStr"/>
+      <c r="N283" s="2" t="inlineStr">
+        <is>
+          <t>diamondbeer@diamondbeverages.fi</t>
+        </is>
+      </c>
+      <c r="O283" s="2" t="inlineStr">
+        <is>
+          <t>+358 10 2310801</t>
+        </is>
+      </c>
+      <c r="P283" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q283" s="2" t="inlineStr">
+        <is>
+          <t>14546792</t>
+        </is>
+      </c>
+      <c r="R283" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/diamond-beverages-oy</t>
+        </is>
+      </c>
+      <c r="S283" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DiamondBeverages/</t>
+        </is>
+      </c>
+      <c r="T283" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/diamondbeverages</t>
+        </is>
+      </c>
+      <c r="U283" s="2" t="inlineStr"/>
+      <c r="V283" s="2" t="inlineStr"/>
+      <c r="W283" s="2" t="inlineStr">
+        <is>
+          <t>Walter Himanen</t>
+        </is>
+      </c>
+      <c r="X283" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y283" s="2" t="inlineStr"/>
+      <c r="Z283" s="2" t="inlineStr"/>
+      <c r="AA283" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/walterhimanen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>Diamond Beverages Oy</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>Diamond Beverages Oy</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="inlineStr">
+        <is>
+          <t>23099</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E284" s="2" t="inlineStr">
+        <is>
+          <t>Vantaa</t>
+        </is>
+      </c>
+      <c r="F284" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>8a Äyritie</t>
+        </is>
+      </c>
+      <c r="H284" s="2" t="inlineStr">
+        <is>
+          <t>01510</t>
+        </is>
+      </c>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>https://diamondbeverages.fi</t>
+        </is>
+      </c>
+      <c r="J284" s="2" t="inlineStr"/>
+      <c r="K284" s="2" t="inlineStr"/>
+      <c r="L284" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M284" s="2" t="inlineStr"/>
+      <c r="N284" s="2" t="inlineStr">
+        <is>
+          <t>diamondbeer@diamondbeverages.fi</t>
+        </is>
+      </c>
+      <c r="O284" s="2" t="inlineStr">
+        <is>
+          <t>+358 10 2310801</t>
+        </is>
+      </c>
+      <c r="P284" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q284" s="2" t="inlineStr">
+        <is>
+          <t>14546792</t>
+        </is>
+      </c>
+      <c r="R284" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/diamond-beverages-oy</t>
+        </is>
+      </c>
+      <c r="S284" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DiamondBeverages/</t>
+        </is>
+      </c>
+      <c r="T284" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/diamondbeverages</t>
+        </is>
+      </c>
+      <c r="U284" s="2" t="inlineStr"/>
+      <c r="V284" s="2" t="inlineStr"/>
+      <c r="W284" s="2" t="inlineStr">
+        <is>
+          <t>Henna Parkkila</t>
+        </is>
+      </c>
+      <c r="X284" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager &amp; Marketing Specialist</t>
+        </is>
+      </c>
+      <c r="Y284" s="2" t="inlineStr"/>
+      <c r="Z284" s="2" t="inlineStr"/>
+      <c r="AA284" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hennaparkkila/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Finland.xlsx
+++ b/BWI/bestwine_output/bestwine_Finland.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA284"/>
+  <dimension ref="A1:AA302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -32637,6 +32637,1952 @@
         </is>
       </c>
     </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F285" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H285" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J285" s="2" t="inlineStr"/>
+      <c r="K285" s="2" t="inlineStr"/>
+      <c r="L285" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M285" s="2" t="inlineStr"/>
+      <c r="N285" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O285" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P285" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q285" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U285" s="2" t="inlineStr"/>
+      <c r="V285" s="2" t="inlineStr"/>
+      <c r="W285" s="2" t="inlineStr">
+        <is>
+          <t>Emmi Leinonen</t>
+        </is>
+      </c>
+      <c r="X285" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager Spirits</t>
+        </is>
+      </c>
+      <c r="Y285" s="2" t="inlineStr"/>
+      <c r="Z285" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA285" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/emmi-leinonen-1690837b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F286" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H286" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J286" s="2" t="inlineStr"/>
+      <c r="K286" s="2" t="inlineStr"/>
+      <c r="L286" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M286" s="2" t="inlineStr"/>
+      <c r="N286" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O286" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P286" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q286" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U286" s="2" t="inlineStr"/>
+      <c r="V286" s="2" t="inlineStr"/>
+      <c r="W286" s="2" t="inlineStr">
+        <is>
+          <t>Andrei Cioanca</t>
+        </is>
+      </c>
+      <c r="X286" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager Spirits</t>
+        </is>
+      </c>
+      <c r="Y286" s="2" t="inlineStr"/>
+      <c r="Z286" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA286" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andreicioanca/</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E287" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F287" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H287" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I287" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J287" s="2" t="inlineStr"/>
+      <c r="K287" s="2" t="inlineStr"/>
+      <c r="L287" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M287" s="2" t="inlineStr"/>
+      <c r="N287" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O287" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P287" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q287" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R287" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S287" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T287" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U287" s="2" t="inlineStr"/>
+      <c r="V287" s="2" t="inlineStr"/>
+      <c r="W287" s="2" t="inlineStr">
+        <is>
+          <t>Sanna Jäppinen</t>
+        </is>
+      </c>
+      <c r="X287" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager Wines</t>
+        </is>
+      </c>
+      <c r="Y287" s="2" t="inlineStr"/>
+      <c r="Z287" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA287" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sanna-j%C3%A4ppinen-07988019/</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E288" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F288" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H288" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I288" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J288" s="2" t="inlineStr"/>
+      <c r="K288" s="2" t="inlineStr"/>
+      <c r="L288" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M288" s="2" t="inlineStr"/>
+      <c r="N288" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O288" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P288" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q288" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R288" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S288" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T288" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U288" s="2" t="inlineStr"/>
+      <c r="V288" s="2" t="inlineStr"/>
+      <c r="W288" s="2" t="inlineStr">
+        <is>
+          <t>Joakim Löfström</t>
+        </is>
+      </c>
+      <c r="X288" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="Y288" s="2" t="inlineStr"/>
+      <c r="Z288" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA288" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/joakim-l%C3%B6fstr%C3%B6m-737232/</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E289" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F289" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G289" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H289" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I289" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J289" s="2" t="inlineStr"/>
+      <c r="K289" s="2" t="inlineStr"/>
+      <c r="L289" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M289" s="2" t="inlineStr"/>
+      <c r="N289" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O289" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P289" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q289" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R289" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S289" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T289" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U289" s="2" t="inlineStr"/>
+      <c r="V289" s="2" t="inlineStr"/>
+      <c r="W289" s="2" t="inlineStr">
+        <is>
+          <t>Timo Laurila</t>
+        </is>
+      </c>
+      <c r="X289" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Director</t>
+        </is>
+      </c>
+      <c r="Y289" s="2" t="inlineStr"/>
+      <c r="Z289" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA289" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/timo-laurila-947078a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F290" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G290" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J290" s="2" t="inlineStr"/>
+      <c r="K290" s="2" t="inlineStr"/>
+      <c r="L290" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M290" s="2" t="inlineStr"/>
+      <c r="N290" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O290" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P290" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q290" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U290" s="2" t="inlineStr"/>
+      <c r="V290" s="2" t="inlineStr"/>
+      <c r="W290" s="2" t="inlineStr">
+        <is>
+          <t>Joni Granath</t>
+        </is>
+      </c>
+      <c r="X290" s="2" t="inlineStr">
+        <is>
+          <t>Head of On-trade</t>
+        </is>
+      </c>
+      <c r="Y290" s="2" t="inlineStr"/>
+      <c r="Z290" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA290" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/joni-granath/</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F291" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G291" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I291" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J291" s="2" t="inlineStr"/>
+      <c r="K291" s="2" t="inlineStr"/>
+      <c r="L291" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M291" s="2" t="inlineStr"/>
+      <c r="N291" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O291" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P291" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q291" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R291" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S291" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T291" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U291" s="2" t="inlineStr"/>
+      <c r="V291" s="2" t="inlineStr"/>
+      <c r="W291" s="2" t="inlineStr">
+        <is>
+          <t>Kiira Signore</t>
+        </is>
+      </c>
+      <c r="X291" s="2" t="inlineStr">
+        <is>
+          <t>Logistics Coordinator</t>
+        </is>
+      </c>
+      <c r="Y291" s="2" t="inlineStr"/>
+      <c r="Z291" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA291" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kiira-signore-31a1a8b6/</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F292" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G292" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J292" s="2" t="inlineStr"/>
+      <c r="K292" s="2" t="inlineStr"/>
+      <c r="L292" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M292" s="2" t="inlineStr"/>
+      <c r="N292" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O292" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P292" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q292" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U292" s="2" t="inlineStr"/>
+      <c r="V292" s="2" t="inlineStr"/>
+      <c r="W292" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Jones</t>
+        </is>
+      </c>
+      <c r="X292" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y292" s="2" t="inlineStr"/>
+      <c r="Z292" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA292" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patrick-jones-162a875/</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E293" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F293" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H293" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J293" s="2" t="inlineStr"/>
+      <c r="K293" s="2" t="inlineStr"/>
+      <c r="L293" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M293" s="2" t="inlineStr"/>
+      <c r="N293" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O293" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P293" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q293" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U293" s="2" t="inlineStr"/>
+      <c r="V293" s="2" t="inlineStr"/>
+      <c r="W293" s="2" t="inlineStr">
+        <is>
+          <t>Hilla Eerikäinen</t>
+        </is>
+      </c>
+      <c r="X293" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Manager Wines</t>
+        </is>
+      </c>
+      <c r="Y293" s="2" t="inlineStr"/>
+      <c r="Z293" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA293" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hilla-eerik%C3%A4inen-22500985/</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F294" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G294" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H294" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I294" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J294" s="2" t="inlineStr"/>
+      <c r="K294" s="2" t="inlineStr"/>
+      <c r="L294" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M294" s="2" t="inlineStr"/>
+      <c r="N294" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O294" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P294" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q294" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R294" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S294" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T294" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U294" s="2" t="inlineStr"/>
+      <c r="V294" s="2" t="inlineStr"/>
+      <c r="W294" s="2" t="inlineStr">
+        <is>
+          <t>Tiina Tuomainen</t>
+        </is>
+      </c>
+      <c r="X294" s="2" t="inlineStr">
+        <is>
+          <t>Product Manager Wines</t>
+        </is>
+      </c>
+      <c r="Y294" s="2" t="inlineStr"/>
+      <c r="Z294" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA294" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tiina-tuomainen-b073a486/</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F295" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G295" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H295" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I295" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J295" s="2" t="inlineStr"/>
+      <c r="K295" s="2" t="inlineStr"/>
+      <c r="L295" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M295" s="2" t="inlineStr"/>
+      <c r="N295" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O295" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P295" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q295" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R295" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S295" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T295" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U295" s="2" t="inlineStr"/>
+      <c r="V295" s="2" t="inlineStr"/>
+      <c r="W295" s="2" t="inlineStr">
+        <is>
+          <t>Timo Vainonen</t>
+        </is>
+      </c>
+      <c r="X295" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager Wines</t>
+        </is>
+      </c>
+      <c r="Y295" s="2" t="inlineStr"/>
+      <c r="Z295" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA295" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/timo-vainonen-348b0521/</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>Beverage Partners Finland Oy</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>4015</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F296" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G296" s="2" t="inlineStr">
+        <is>
+          <t>11 Vilhonvuorenkatu</t>
+        </is>
+      </c>
+      <c r="H296" s="2" t="inlineStr">
+        <is>
+          <t>00500</t>
+        </is>
+      </c>
+      <c r="I296" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="J296" s="2" t="inlineStr"/>
+      <c r="K296" s="2" t="inlineStr"/>
+      <c r="L296" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M296" s="2" t="inlineStr"/>
+      <c r="N296" s="2" t="inlineStr">
+        <is>
+          <t>myynti@bpf-finland.fi</t>
+        </is>
+      </c>
+      <c r="O296" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 6229190</t>
+        </is>
+      </c>
+      <c r="P296" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q296" s="2" t="inlineStr">
+        <is>
+          <t>15922198</t>
+        </is>
+      </c>
+      <c r="R296" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/beverage-partners-finland/</t>
+        </is>
+      </c>
+      <c r="S296" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="T296" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/viinisuositus/</t>
+        </is>
+      </c>
+      <c r="U296" s="2" t="inlineStr"/>
+      <c r="V296" s="2" t="inlineStr"/>
+      <c r="W296" s="2" t="inlineStr">
+        <is>
+          <t>Kalle Sukanen</t>
+        </is>
+      </c>
+      <c r="X296" s="2" t="inlineStr">
+        <is>
+          <t>Senior Brand Manager Spirits</t>
+        </is>
+      </c>
+      <c r="Y296" s="2" t="inlineStr"/>
+      <c r="Z296" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA296" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kalle-sukanen-33715a11/</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>Oy Winital S.p.a.</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>Oy Winital S.p.a.</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>4073</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G297" s="2" t="inlineStr">
+        <is>
+          <t>2 Korkeavuorenkatu</t>
+        </is>
+      </c>
+      <c r="H297" s="2" t="inlineStr">
+        <is>
+          <t>00140</t>
+        </is>
+      </c>
+      <c r="I297" s="2" t="inlineStr">
+        <is>
+          <t>http://winital.fi</t>
+        </is>
+      </c>
+      <c r="J297" s="2" t="inlineStr"/>
+      <c r="K297" s="2" t="inlineStr"/>
+      <c r="L297" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M297" s="2" t="inlineStr"/>
+      <c r="N297" s="2" t="inlineStr">
+        <is>
+          <t>winital@yahoo.com</t>
+        </is>
+      </c>
+      <c r="O297" s="2" t="inlineStr">
+        <is>
+          <t>+358 9 68424840</t>
+        </is>
+      </c>
+      <c r="P297" s="2" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="Q297" s="2" t="inlineStr">
+        <is>
+          <t>09460388</t>
+        </is>
+      </c>
+      <c r="R297" s="2" t="inlineStr"/>
+      <c r="S297" s="2" t="inlineStr"/>
+      <c r="T297" s="2" t="inlineStr"/>
+      <c r="U297" s="2" t="inlineStr"/>
+      <c r="V297" s="2" t="inlineStr"/>
+      <c r="W297" s="2" t="inlineStr">
+        <is>
+          <t>Petri Viglione</t>
+        </is>
+      </c>
+      <c r="X297" s="2" t="inlineStr">
+        <is>
+          <t>Wine Importer</t>
+        </is>
+      </c>
+      <c r="Y297" s="2" t="inlineStr"/>
+      <c r="Z297" s="2" t="inlineStr"/>
+      <c r="AA297" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/petri-viglione-45b1751b8/?originalSubdomain=fi</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>Cisa Drinks Oy</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>Cisa Drinks Oy</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>4020</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>Espoo</t>
+        </is>
+      </c>
+      <c r="F298" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G298" s="2" t="inlineStr">
+        <is>
+          <t>15 Kavallinmäki</t>
+        </is>
+      </c>
+      <c r="H298" s="2" t="inlineStr">
+        <is>
+          <t>02710</t>
+        </is>
+      </c>
+      <c r="I298" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cisa.fi</t>
+        </is>
+      </c>
+      <c r="J298" s="2" t="inlineStr"/>
+      <c r="K298" s="2" t="inlineStr"/>
+      <c r="L298" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M298" s="2" t="inlineStr"/>
+      <c r="N298" s="2" t="inlineStr">
+        <is>
+          <t>info@cisa.fi</t>
+        </is>
+      </c>
+      <c r="O298" s="2" t="inlineStr"/>
+      <c r="P298" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q298" s="2" t="inlineStr">
+        <is>
+          <t>18254850</t>
+        </is>
+      </c>
+      <c r="R298" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cisa-drinks-oy/</t>
+        </is>
+      </c>
+      <c r="S298" s="2" t="inlineStr"/>
+      <c r="T298" s="2" t="inlineStr"/>
+      <c r="U298" s="2" t="inlineStr"/>
+      <c r="V298" s="2" t="inlineStr"/>
+      <c r="W298" s="2" t="inlineStr">
+        <is>
+          <t>Risto Suomio</t>
+        </is>
+      </c>
+      <c r="X298" s="2" t="inlineStr">
+        <is>
+          <t>Partner, Purchasing</t>
+        </is>
+      </c>
+      <c r="Y298" s="2" t="inlineStr"/>
+      <c r="Z298" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA298" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/risto-suomio-2366702/</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>Cisa Drinks Oy</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>Cisa Drinks Oy</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>4020</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>Espoo</t>
+        </is>
+      </c>
+      <c r="F299" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>15 Kavallinmäki</t>
+        </is>
+      </c>
+      <c r="H299" s="2" t="inlineStr">
+        <is>
+          <t>02710</t>
+        </is>
+      </c>
+      <c r="I299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cisa.fi</t>
+        </is>
+      </c>
+      <c r="J299" s="2" t="inlineStr"/>
+      <c r="K299" s="2" t="inlineStr"/>
+      <c r="L299" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M299" s="2" t="inlineStr"/>
+      <c r="N299" s="2" t="inlineStr">
+        <is>
+          <t>info@cisa.fi</t>
+        </is>
+      </c>
+      <c r="O299" s="2" t="inlineStr"/>
+      <c r="P299" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q299" s="2" t="inlineStr">
+        <is>
+          <t>18254850</t>
+        </is>
+      </c>
+      <c r="R299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cisa-drinks-oy/</t>
+        </is>
+      </c>
+      <c r="S299" s="2" t="inlineStr"/>
+      <c r="T299" s="2" t="inlineStr"/>
+      <c r="U299" s="2" t="inlineStr"/>
+      <c r="V299" s="2" t="inlineStr"/>
+      <c r="W299" s="2" t="inlineStr">
+        <is>
+          <t>Toni Vaskivuo</t>
+        </is>
+      </c>
+      <c r="X299" s="2" t="inlineStr">
+        <is>
+          <t>Logistics Controller, Buyer</t>
+        </is>
+      </c>
+      <c r="Y299" s="2" t="inlineStr"/>
+      <c r="Z299" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA299" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/toni-vaskivuo-604727a4/</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>Wineworld Finland Oy</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>Wineworld Finland Oy</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>35602</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E300" s="2" t="inlineStr">
+        <is>
+          <t>Helsinki</t>
+        </is>
+      </c>
+      <c r="F300" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>1 Kaapeliaukio</t>
+        </is>
+      </c>
+      <c r="H300" s="2" t="inlineStr">
+        <is>
+          <t>00180</t>
+        </is>
+      </c>
+      <c r="I300" s="2" t="inlineStr">
+        <is>
+          <t>https://wineworld.fi</t>
+        </is>
+      </c>
+      <c r="J300" s="2" t="inlineStr"/>
+      <c r="K300" s="2" t="inlineStr"/>
+      <c r="L300" s="2" t="inlineStr"/>
+      <c r="M300" s="2" t="inlineStr"/>
+      <c r="N300" s="2" t="inlineStr">
+        <is>
+          <t>info@wineworld.fi</t>
+        </is>
+      </c>
+      <c r="O300" s="2" t="inlineStr"/>
+      <c r="P300" s="2" t="inlineStr"/>
+      <c r="Q300" s="2" t="inlineStr"/>
+      <c r="R300" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wineworld-finland/</t>
+        </is>
+      </c>
+      <c r="S300" s="2" t="inlineStr"/>
+      <c r="T300" s="2" t="inlineStr"/>
+      <c r="U300" s="2" t="inlineStr"/>
+      <c r="V300" s="2" t="inlineStr"/>
+      <c r="W300" s="2" t="inlineStr"/>
+      <c r="X300" s="2" t="inlineStr"/>
+      <c r="Y300" s="2" t="inlineStr"/>
+      <c r="Z300" s="2" t="inlineStr"/>
+      <c r="AA300" s="2" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>Diamond Beverages Oy</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>Diamond Beverages Oy</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>23099</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E301" s="2" t="inlineStr">
+        <is>
+          <t>Vantaa</t>
+        </is>
+      </c>
+      <c r="F301" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G301" s="2" t="inlineStr">
+        <is>
+          <t>8a Äyritie</t>
+        </is>
+      </c>
+      <c r="H301" s="2" t="inlineStr">
+        <is>
+          <t>01510</t>
+        </is>
+      </c>
+      <c r="I301" s="2" t="inlineStr">
+        <is>
+          <t>https://diamondbeverages.fi</t>
+        </is>
+      </c>
+      <c r="J301" s="2" t="inlineStr"/>
+      <c r="K301" s="2" t="inlineStr"/>
+      <c r="L301" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M301" s="2" t="inlineStr"/>
+      <c r="N301" s="2" t="inlineStr">
+        <is>
+          <t>diamondbeer@diamondbeverages.fi</t>
+        </is>
+      </c>
+      <c r="O301" s="2" t="inlineStr">
+        <is>
+          <t>+358 10 2310801</t>
+        </is>
+      </c>
+      <c r="P301" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q301" s="2" t="inlineStr">
+        <is>
+          <t>14546792</t>
+        </is>
+      </c>
+      <c r="R301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/diamond-beverages-oy</t>
+        </is>
+      </c>
+      <c r="S301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DiamondBeverages/</t>
+        </is>
+      </c>
+      <c r="T301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/diamondbeverages</t>
+        </is>
+      </c>
+      <c r="U301" s="2" t="inlineStr"/>
+      <c r="V301" s="2" t="inlineStr"/>
+      <c r="W301" s="2" t="inlineStr">
+        <is>
+          <t>Walter Himanen</t>
+        </is>
+      </c>
+      <c r="X301" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y301" s="2" t="inlineStr"/>
+      <c r="Z301" s="2" t="inlineStr"/>
+      <c r="AA301" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/walterhimanen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>Diamond Beverages Oy</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>Diamond Beverages Oy</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>23099</t>
+        </is>
+      </c>
+      <c r="D302" s="2" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="E302" s="2" t="inlineStr">
+        <is>
+          <t>Vantaa</t>
+        </is>
+      </c>
+      <c r="F302" s="2" t="inlineStr">
+        <is>
+          <t>Uusimaa, Helsinki</t>
+        </is>
+      </c>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>8a Äyritie</t>
+        </is>
+      </c>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>01510</t>
+        </is>
+      </c>
+      <c r="I302" s="2" t="inlineStr">
+        <is>
+          <t>https://diamondbeverages.fi</t>
+        </is>
+      </c>
+      <c r="J302" s="2" t="inlineStr"/>
+      <c r="K302" s="2" t="inlineStr"/>
+      <c r="L302" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M302" s="2" t="inlineStr"/>
+      <c r="N302" s="2" t="inlineStr">
+        <is>
+          <t>diamondbeer@diamondbeverages.fi</t>
+        </is>
+      </c>
+      <c r="O302" s="2" t="inlineStr">
+        <is>
+          <t>+358 10 2310801</t>
+        </is>
+      </c>
+      <c r="P302" s="2" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="Q302" s="2" t="inlineStr">
+        <is>
+          <t>14546792</t>
+        </is>
+      </c>
+      <c r="R302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/diamond-beverages-oy</t>
+        </is>
+      </c>
+      <c r="S302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DiamondBeverages/</t>
+        </is>
+      </c>
+      <c r="T302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/diamondbeverages</t>
+        </is>
+      </c>
+      <c r="U302" s="2" t="inlineStr"/>
+      <c r="V302" s="2" t="inlineStr"/>
+      <c r="W302" s="2" t="inlineStr">
+        <is>
+          <t>Henna Parkkila</t>
+        </is>
+      </c>
+      <c r="X302" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager &amp; Marketing Specialist</t>
+        </is>
+      </c>
+      <c r="Y302" s="2" t="inlineStr"/>
+      <c r="Z302" s="2" t="inlineStr"/>
+      <c r="AA302" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hennaparkkila/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
